--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>46196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45832</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>45999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>44930</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>45901</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45004</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45002</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45103</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45050</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45303</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46142</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45110</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45961</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45337</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45903</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45050</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>46069</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>45387</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46188</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45631</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>46112</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>46125</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>45905</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45917</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45085</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>46251</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45625</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45603</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>46283</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45561</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45847</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45050</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45474</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>45611</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>46101</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44869</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44468</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44585</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44687</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44670</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44875</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44458</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44483</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44559</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44691</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44526</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44462</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44659</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44629</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44502</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44503</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44462</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44497</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44806</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44874</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44742</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44629</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44501</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44571</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44599</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44491</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44588</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44476</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44516</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44623</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44460</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44484</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44719</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44825</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44634</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11963,7 +11963,7 @@
         <v>44627</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44847</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12182,7 +12182,7 @@
         <v>44475</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44809</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44524</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44698</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44621</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44859</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44743</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44742</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44480</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44466</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44837</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44706</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44608</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44579</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44494</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13282,7 +13282,7 @@
         <v>44687</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44466</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44596</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44467</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44592</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44503</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44711</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44804</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>44614</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44657</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>44858</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44875</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45400</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45035</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45456</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45257</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44886</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45196</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>44491</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>44967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45615</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45180</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45393</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45108</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>44875</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45531</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45643</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45387</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>44747</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>44998</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44860</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>44741</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>45674</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45373</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>44946</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45315</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44939</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>44890</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45215</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>44672</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>44937</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45458</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45051</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45019</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45166</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45034</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45362</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44553</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45578</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45142</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45159</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>45198</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44986</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44692</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44847</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44847</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45002</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45028</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>45075</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>45266</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45079</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17959,7 +17959,7 @@
         <v>45020</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>44545</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45315</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45162</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44879</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45586</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44691</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45328</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>45743</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>44706</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45028</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45483</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45727</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45335</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44757</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45324</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45707</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>44930</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>44851</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45328</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>44593</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45107</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45541</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45234</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45568</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45028</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45028</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>44636</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>44988</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44584</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45537</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45365</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45443</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>44512</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45085</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45475</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44587</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45001</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45278</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45610</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45742</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45553</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>44592</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45069</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45532</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45532</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45218</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45204</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>44974</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45600</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45245</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45532</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45254</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>45013</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45537</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45218</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45048</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44609</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>44609</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>44825</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45411</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45085</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45085</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45697</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44586</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45309</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>44820</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>44516</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23084,7 +23084,7 @@
         <v>44725</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23157,7 +23157,7 @@
         <v>45225</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
         <v>45308</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23303,7 +23303,7 @@
         <v>45443</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>44523</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44638</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>45512</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45361</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45013</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>45013</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45162</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>44619</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>44636</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45887</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45342</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45707</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45685</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45095</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45576</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45784</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45526</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45894</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>44860</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45880</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>45923</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45050</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45104</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>45251</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45316</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45715</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45968</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45250</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45749</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45084</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>44474</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45645</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>44461</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45335</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45664</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45334</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>45981</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45370</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45884</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45093</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45980</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45827</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45251</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44551</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45737</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45784</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45784</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45789</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45631</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45846</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45334</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45358</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45908</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45133</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>44747</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45092</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>44874</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>45180</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45166</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45166</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45210</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45917</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>45647</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>45415</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45091</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45918</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>45156</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>45917</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>45923</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45012</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28705,7 +28705,7 @@
         <v>45923</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28778,7 +28778,7 @@
         <v>45923</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28851,7 +28851,7 @@
         <v>45159</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28924,7 +28924,7 @@
         <v>45887</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45747</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45925</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45728</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45929</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45929</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>45350</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29435,7 +29435,7 @@
         <v>45035</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45035</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>45930</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>44742</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45343</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45106</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>44628</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>45092</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45089</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>44636</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45148</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>45937</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45937</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45645</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45945</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45945</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45945</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45580</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45217</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45713</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>45212</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45631</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>46148</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45645</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46150</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45173</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>45579</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>45340</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>44911</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45013</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45538</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45727</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45407</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45735</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45954</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45495</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45957</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45958</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32355,7 +32355,7 @@
         <v>45958</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45958</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32501,7 +32501,7 @@
         <v>45958</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32647,7 +32647,7 @@
         <v>45118</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32720,7 +32720,7 @@
         <v>45106</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32793,7 +32793,7 @@
         <v>45961</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         <v>45002</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>44936</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33012,7 +33012,7 @@
         <v>44753</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33085,7 +33085,7 @@
         <v>45961</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45961</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45971</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>45194</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>44862</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>45106</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45630</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45938</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45551</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45117</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45168</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45351</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45972</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45619</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45154</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>44530</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45978</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>44473</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>45537</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>46097</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45981</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45832</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45012</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34764,7 +34764,7 @@
         <v>44809</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34837,7 +34837,7 @@
         <v>45133</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>46077</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>44756</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45077</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>44942</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45604</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45107</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44728</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45809</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45695</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35567,7 +35567,7 @@
         <v>46125</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35640,7 +35640,7 @@
         <v>46158</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>45469</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45699</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45809</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45846</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36010,7 +36010,7 @@
         <v>44981</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36083,7 +36083,7 @@
         <v>45610</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36156,7 +36156,7 @@
         <v>46158</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36229,7 +36229,7 @@
         <v>46158</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36302,7 +36302,7 @@
         <v>46158</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36375,7 +36375,7 @@
         <v>46158</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36448,7 +36448,7 @@
         <v>44596</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36526,7 +36526,7 @@
         <v>46158</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36599,7 +36599,7 @@
         <v>46037</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>46058</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45610</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36818,7 +36818,7 @@
         <v>44876</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36891,7 +36891,7 @@
         <v>45551</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36964,7 +36964,7 @@
         <v>46162</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37037,7 +37037,7 @@
         <v>44837</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37110,7 +37110,7 @@
         <v>45127</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37183,7 +37183,7 @@
         <v>45846</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>45512</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>46162</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45166</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>46163</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>44543</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>46162</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45554</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45261</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>46000</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45366</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46164</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45202</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45075</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46167</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>44930</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>46164</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>46164</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45013</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>46007</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>46007</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>45082</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45014</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45085</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45107</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44614</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>46169</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45007</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45007</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45215</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45551</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>44691</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>46027</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45085</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44799</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44641</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>45077</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46031</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>45537</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>45538</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>45170</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45166</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45251</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44631</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45463</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45463</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45057</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>44754</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>45092</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>45009</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>46042</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45455</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>46042</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>46042</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45238</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>44511</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>44580</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>45315</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46055</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>46049</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>45043</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>46051</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>46051</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>46176</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>46176</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46051</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>46052</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45113</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>44881</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>46056</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>46177</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>44920</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42444,7 +42444,7 @@
         <v>45055</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>46177</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42590,7 +42590,7 @@
         <v>46177</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>46069</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>46066</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>44545</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>46181</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42955,7 +42955,7 @@
         <v>46182</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>46181</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43101,7 +43101,7 @@
         <v>46181</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43174,7 +43174,7 @@
         <v>44988</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>44960</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43320,7 +43320,7 @@
         <v>45279</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43393,7 +43393,7 @@
         <v>45387</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45080</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>46183</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43612,7 +43612,7 @@
         <v>45238</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43685,7 +43685,7 @@
         <v>45247</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>46056</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43831,7 +43831,7 @@
         <v>45243</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43904,7 +43904,7 @@
         <v>45105</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45106</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44050,7 +44050,7 @@
         <v>45499</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45165</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44196,7 +44196,7 @@
         <v>46087</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>46188</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>46188</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44420,7 +44420,7 @@
         <v>46185</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45524</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>45218</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>44866</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>46092</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44790,7 +44790,7 @@
         <v>45264</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>45188</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>45093</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45009,7 +45009,7 @@
         <v>46097</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45082,7 +45082,7 @@
         <v>45113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45155,7 +45155,7 @@
         <v>44914</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45321</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45301,7 +45301,7 @@
         <v>45127</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45238</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45447,7 +45447,7 @@
         <v>45334</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45520,7 +45520,7 @@
         <v>46106</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>45662</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45531</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>44991</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45817,7 +45817,7 @@
         <v>44624</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>44939</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>44939</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45393</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45278</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46182,7 +46182,7 @@
         <v>45204</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46255,7 +46255,7 @@
         <v>46177</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46328,7 +46328,7 @@
         <v>46112</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>46112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>45698</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45178</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>44585</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45062</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46766,7 +46766,7 @@
         <v>44893</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>46113</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46912,7 +46912,7 @@
         <v>46113</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>45394</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>46113</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>46113</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>46113</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47277,7 +47277,7 @@
         <v>46113</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>46113</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>46113</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47496,7 +47496,7 @@
         <v>45344</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47569,7 +47569,7 @@
         <v>44820</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>46199</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45673</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47788,7 +47788,7 @@
         <v>45309</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45142</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>46125</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>46199</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48080,7 +48080,7 @@
         <v>44840</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45577</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48226,7 +48226,7 @@
         <v>45094</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48299,7 +48299,7 @@
         <v>45208</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>45393</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>46199</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>46245</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48591,7 +48591,7 @@
         <v>45161</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>45531</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48737,7 +48737,7 @@
         <v>46246</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>45140</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45344</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45524</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49029,7 +49029,7 @@
         <v>46246</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45218</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>44757</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49248,7 +49248,7 @@
         <v>44619</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45195</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45180</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45637</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>45915</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45911</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45181</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>44825</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45783</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45985</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>46246</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>45309</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50124,7 +50124,7 @@
         <v>45182</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45747</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50270,7 +50270,7 @@
         <v>45090</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50343,7 +50343,7 @@
         <v>45324</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50416,7 +50416,7 @@
         <v>45223</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>45170</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>45042</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46246</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>45406</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>45162</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>46246</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>44893</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45092</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46206</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>44930</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>46206</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>44461</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45092</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51438,7 +51438,7 @@
         <v>46253</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>46253</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>45454</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45169</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>46177</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>45573</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45761</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>44517</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52022,7 +52022,7 @@
         <v>45027</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52095,7 +52095,7 @@
         <v>46254</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52168,7 +52168,7 @@
         <v>45194</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52241,7 +52241,7 @@
         <v>46254</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45309</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52387,7 +52387,7 @@
         <v>45838</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52460,7 +52460,7 @@
         <v>44700</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52533,7 +52533,7 @@
         <v>45674</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52606,7 +52606,7 @@
         <v>45183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>44603</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46258</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45225</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52898,7 +52898,7 @@
         <v>45393</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>44616</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53044,7 +53044,7 @@
         <v>46258</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>46209</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>46209</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53263,7 +53263,7 @@
         <v>45174</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45070</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53409,7 +53409,7 @@
         <v>45037</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53482,7 +53482,7 @@
         <v>45092</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53555,7 +53555,7 @@
         <v>44909</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53628,7 +53628,7 @@
         <v>45076</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53701,7 +53701,7 @@
         <v>44900</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45266</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53847,7 +53847,7 @@
         <v>46070</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53920,7 +53920,7 @@
         <v>45571</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>45565</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>44722</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>44903</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>45154</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54285,7 +54285,7 @@
         <v>46265</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54358,7 +54358,7 @@
         <v>44711</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>44693</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54504,7 +54504,7 @@
         <v>44581</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54577,7 +54577,7 @@
         <v>45075</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54650,7 +54650,7 @@
         <v>45616</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54723,7 +54723,7 @@
         <v>45062</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54796,7 +54796,7 @@
         <v>46188</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>45113</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46267</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55015,7 +55015,7 @@
         <v>46268</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>45672</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55161,7 +55161,7 @@
         <v>45301</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55234,7 +55234,7 @@
         <v>45030</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45348</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55380,7 +55380,7 @@
         <v>44748</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55453,7 +55453,7 @@
         <v>45775</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55526,7 +55526,7 @@
         <v>45048</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55599,7 +55599,7 @@
         <v>46268</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55672,7 +55672,7 @@
         <v>45028</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55745,7 +55745,7 @@
         <v>45075</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55818,7 +55818,7 @@
         <v>45604</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55891,7 +55891,7 @@
         <v>45495</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55964,7 +55964,7 @@
         <v>45075</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>46269</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56110,7 +56110,7 @@
         <v>45538</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56183,7 +56183,7 @@
         <v>46230</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56256,7 +56256,7 @@
         <v>45594</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56329,7 +56329,7 @@
         <v>45555</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45344</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56480,7 +56480,7 @@
         <v>45499</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56553,7 +56553,7 @@
         <v>45372</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56626,7 +56626,7 @@
         <v>45573</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45621</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>46270</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56845,7 +56845,7 @@
         <v>46272</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56918,7 +56918,7 @@
         <v>46111</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56991,7 +56991,7 @@
         <v>45783</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57064,7 +57064,7 @@
         <v>45783</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45387</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>46265</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46274</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>46182</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>45624</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57502,7 +57502,7 @@
         <v>45674</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57575,7 +57575,7 @@
         <v>45714</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57648,7 +57648,7 @@
         <v>45631</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57721,7 +57721,7 @@
         <v>45785</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57794,7 +57794,7 @@
         <v>44496</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45656</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57940,7 +57940,7 @@
         <v>45453</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58013,7 +58013,7 @@
         <v>45754</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58086,7 +58086,7 @@
         <v>45691</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58159,7 +58159,7 @@
         <v>45532</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58232,7 +58232,7 @@
         <v>45384</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58305,7 +58305,7 @@
         <v>46280</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58378,7 +58378,7 @@
         <v>45540</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58451,7 +58451,7 @@
         <v>46239</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58524,7 +58524,7 @@
         <v>46283</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58597,7 +58597,7 @@
         <v>45797</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58670,7 +58670,7 @@
         <v>45797</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58743,7 +58743,7 @@
         <v>45796</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58816,7 +58816,7 @@
         <v>45693</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58889,7 +58889,7 @@
         <v>45581</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58962,7 +58962,7 @@
         <v>46241</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59035,7 +59035,7 @@
         <v>45770</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59108,7 +59108,7 @@
         <v>46283</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59181,7 +59181,7 @@
         <v>46275</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59283,7 +59283,7 @@
         <v>45632</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59356,7 +59356,7 @@
         <v>46241</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59429,7 +59429,7 @@
         <v>45012</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45393</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59575,7 +59575,7 @@
         <v>45537</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59648,7 +59648,7 @@
         <v>45826</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59721,7 +59721,7 @@
         <v>45812</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59794,7 +59794,7 @@
         <v>45839</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59867,7 +59867,7 @@
         <v>45711</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59940,7 +59940,7 @@
         <v>45256</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45812</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>45695</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60159,7 +60159,7 @@
         <v>45602</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60232,7 +60232,7 @@
         <v>45602</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60305,7 +60305,7 @@
         <v>45735</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60378,7 +60378,7 @@
         <v>45789</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>45749</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60524,7 +60524,7 @@
         <v>45873</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>45875</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45875</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>45883</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60816,7 +60816,7 @@
         <v>45883</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60889,7 +60889,7 @@
         <v>44825</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>43938</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>44110</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>44831</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45188</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61269,7 +61269,7 @@
         <v>45250</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>44960</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61415,7 +61415,7 @@
         <v>44959</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61488,7 +61488,7 @@
         <v>44981</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61561,7 +61561,7 @@
         <v>45373</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61634,7 +61634,7 @@
         <v>44959</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61707,7 +61707,7 @@
         <v>44972</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>45155</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>45611</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45271</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61999,7 +61999,7 @@
         <v>45474</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62072,7 +62072,7 @@
         <v>44462</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62145,7 +62145,7 @@
         <v>45646</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62218,7 +62218,7 @@
         <v>45734</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62291,7 +62291,7 @@
         <v>45702</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62364,7 +62364,7 @@
         <v>45719</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62437,7 +62437,7 @@
         <v>45734</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>45460</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>46045</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62656,7 +62656,7 @@
         <v>46064</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62729,7 +62729,7 @@
         <v>46070</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62802,7 +62802,7 @@
         <v>46097</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>46099</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>46099</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -63021,7 +63021,7 @@
         <v>46105</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -63094,7 +63094,7 @@
         <v>46164</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -63167,7 +63167,7 @@
         <v>46260</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>46196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45050</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45012</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45961</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46125</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45004</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>45917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45905</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45561</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45103</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46188</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45631</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45303</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>46069</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45337</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45387</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44830</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44483</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44559</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44691</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44526</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44659</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44676</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44502</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44719</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44503</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44497</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44806</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44874</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44742</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44629</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44501</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44571</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44599</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44491</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44588</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44484</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44719</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44825</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44634</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44540</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44809</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44524</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44698</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44480</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44466</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44837</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44494</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44687</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44466</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44592</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44608</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44503</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44614</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44657</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44875</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45180</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45334</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45715</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45247</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45334</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44825</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45407</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45208</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45321</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45092</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44847</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45393</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45387</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45411</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45455</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45458</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45257</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45315</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45443</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46027</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45309</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46031</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45797</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44473</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45749</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44939</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44939</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45475</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45512</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>46042</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>46042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45499</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44893</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45373</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45524</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45647</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46055</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45551</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44584</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45674</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46049</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44988</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45077</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46051</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45908</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44614</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45693</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44747</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46051</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>46052</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46056</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45632</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44691</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44587</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45007</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45012</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45742</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45918</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44939</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45028</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45028</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46066</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45917</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45923</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45393</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44692</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45923</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45565</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44911</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45747</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45261</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45637</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45925</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45930</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46056</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44920</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46087</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45324</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45037</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45251</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45937</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45937</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45057</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>46097</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45142</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45218</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45085</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44756</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45945</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45945</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46106</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45586</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44619</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45009</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45279</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44967</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45350</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45309</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45316</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44700</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>46113</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>46113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>46112</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45958</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45092</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45308</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45961</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45961</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45107</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45079</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45938</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45604</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45266</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44757</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45117</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45972</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45537</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45783</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45631</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45894</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45911</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45923</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45685</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45784</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45846</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45846</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45968</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45784</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45884</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44747</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45664</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44474</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44820</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45554</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45028</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45148</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>44840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45188</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45784</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45204</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46007</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44748</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45215</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45789</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>44890</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44530</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45080</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45043</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45576</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45075</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45826</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45077</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45537</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45166</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45012</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44636</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>45553</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45532</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45735</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45264</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>44860</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45234</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45085</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45538</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45538</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>46148</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>46150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45812</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45541</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45406</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>46097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45013</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>44609</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46077</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45256</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45832</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45809</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46158</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46058</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45809</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46158</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46158</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46158</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46158</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>46158</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45106</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45699</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46037</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45108</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45013</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45711</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45050</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46162</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46162</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46162</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45695</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44837</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>46164</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44545</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>46164</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>45344</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>44551</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>45106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>45393</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>46167</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45387</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45551</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45107</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>46169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>45107</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45469</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45107</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45002</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45602</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45602</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45789</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44879</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45020</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45537</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>46177</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>46176</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45156</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45394</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46177</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46176</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45531</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45035</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45014</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45524</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46181</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45084</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45106</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45573</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45127</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45415</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46181</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>44512</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46183</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45076</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46185</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45170</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45278</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>46188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44581</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45749</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>46188</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45873</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45335</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45334</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>44511</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45875</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45875</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45028</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46177</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45218</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>46199</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45673</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46199</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45218</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44553</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45075</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44641</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44523</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45328</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>44624</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45747</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>45162</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45315</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>44619</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44799</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45610</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45883</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45883</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45366</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45092</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>44586</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45170</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45194</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45095</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45643</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44754</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>46206</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>46206</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45062</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45196</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45090</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46253</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>46253</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45198</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44725</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>44706</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45707</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>46254</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45761</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>46258</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45210</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45775</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45531</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45578</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46258</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>45166</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45173</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>44616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44728</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45838</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45697</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44742</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>44809</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>44711</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46070</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>44757</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>44631</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44420,7 +44420,7 @@
         <v>45463</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45463</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>46265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45180</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44820</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>46188</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44722</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45309</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>44930</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45365</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45630</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>46111</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>46270</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45361</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>44862</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>44886</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>46274</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>44946</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46245,7 +46245,7 @@
         <v>45348</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>44851</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46391,7 +46391,7 @@
         <v>44753</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>46230</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45309</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45278</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45159</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>44874</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>45166</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>46280</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44672</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44636</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44585</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45140</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45070</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45645</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45301</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45335</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45215</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45089</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45981</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>44893</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>46112</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         <v>44517</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45727</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45495</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>45887</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>46283</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45013</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45610</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46182</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45351</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45092</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46069</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45456</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>44543</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46239</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45238</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45495</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45243</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45202</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>44603</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45358</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45344</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>44491</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45783</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>46275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45923</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>46241</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46283</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45393</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45362</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45887</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>44869</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>44967</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45735</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45754</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>44909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45180</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45737</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46241</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46000</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45971</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45019</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45069</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45093</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45183</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46245</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46287</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>44691</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45075</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46209</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46209</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>46246</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45579</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>46246</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45002</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45169</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>46246</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44741</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44937</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>45217</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44580</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>46246</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45981</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45166</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45035</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45013</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45013</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45225</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>46290</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>44930</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45568</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45531</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>44960</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45580</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45104</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44942</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>45051</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>44593</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45154</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>44875</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>44914</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>45106</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45615</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>45537</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>44900</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>45195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>44998</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45324</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>44592</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45012</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45166</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45085</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45340</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>45159</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45048</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>44903</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45370</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45674</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45454</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>44991</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45028</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>45551</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>45168</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45672</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45537</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45254</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>45174</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45662</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45251</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45223</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45094</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45212</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45619</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>45707</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45443</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57010,7 +57010,7 @@
         <v>45328</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45034</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>45218</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45393</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57302,7 +57302,7 @@
         <v>45154</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57375,7 +57375,7 @@
         <v>44545</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45106</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45085</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57594,7 +57594,7 @@
         <v>45085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45082</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45483</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45118</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45571</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45007</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45727</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45315</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>45631</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>45250</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>45698</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>45695</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>45600</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>45342</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45165</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58762,7 +58762,7 @@
         <v>45225</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>45075</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>45538</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>45604</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45621</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45555</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>45075</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45344</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59351,7 +59351,7 @@
         <v>45372</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59424,7 +59424,7 @@
         <v>45499</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45594</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45573</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>45387</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45783</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>45540</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45384</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45624</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45714</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45631</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45691</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45532</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45453</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45785</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45656</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45674</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>44496</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60665,7 +60665,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>44110</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>43938</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>44825</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45188</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45373</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45611</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45271</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61483,7 +61483,7 @@
         <v>45474</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61556,7 +61556,7 @@
         <v>45646</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61702,7 +61702,7 @@
         <v>45702</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61775,7 +61775,7 @@
         <v>45719</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45734</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>45460</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46064</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>46097</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>46099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>46099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>46105</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46164</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46260</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>44972</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>44960</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45250</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>44981</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>46045</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>46196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44467</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45050</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45579</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45012</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>46112</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45961</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46125</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>46070</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5436,7 +5436,7 @@
         <v>45004</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>45917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>45903</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45905</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>45561</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>45103</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45847</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46188</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45631</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45303</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45002</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>46069</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45337</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45110</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45387</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45625</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45603</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>44468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8970,7 +8970,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44830</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44483</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44501</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44559</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44691</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         <v>44526</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
         <v>44659</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>44676</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>44629</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44502</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44719</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>44503</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44497</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44806</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44624</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>44874</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44742</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44629</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44501</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44571</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10868,7 +10868,7 @@
         <v>44599</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>44491</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11014,7 +11014,7 @@
         <v>44588</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
         <v>44476</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44623</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44484</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>44719</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11452,7 +11452,7 @@
         <v>44825</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         <v>44627</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44634</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>44847</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>44540</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44809</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44524</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44698</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12114,7 +12114,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44743</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44480</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44466</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44837</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44706</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44579</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44494</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44687</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44466</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44596</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44592</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>44608</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         <v>44503</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44711</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44804</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44614</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13652,7 +13652,7 @@
         <v>44657</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>44858</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13798,7 +13798,7 @@
         <v>44875</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>45180</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>45334</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14090,7 +14090,7 @@
         <v>45715</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>45247</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14236,7 +14236,7 @@
         <v>45512</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>45334</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14455,7 +14455,7 @@
         <v>45042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>44825</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>44881</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>44825</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>45407</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45208</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45321</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45092</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44860</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44847</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45393</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45387</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15550,7 +15550,7 @@
         <v>45411</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15696,7 +15696,7 @@
         <v>45455</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>44866</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45458</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45257</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45315</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45127</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45443</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>46027</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45309</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45113</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46031</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45797</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44473</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16937,7 +16937,7 @@
         <v>45581</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>45749</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44939</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44939</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>45475</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>45512</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>46042</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44609</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>46042</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46042</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45499</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44893</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45373</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>45524</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44592</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>45647</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>46055</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45162</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>45551</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>44584</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18548,7 +18548,7 @@
         <v>45674</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>46049</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>44988</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45077</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46051</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45908</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44614</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19132,7 +19132,7 @@
         <v>45693</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>44747</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>46051</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45645</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>45645</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>46051</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>46052</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>46056</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45632</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44691</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>44587</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45007</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45012</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45616</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45742</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>45918</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>44939</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45028</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20519,7 @@
         <v>45028</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>46066</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45917</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45923</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45393</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>44692</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45923</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45565</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>44911</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45747</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
         <v>45261</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45637</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45925</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45930</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45929</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21614,7 +21614,7 @@
         <v>45929</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46056</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>44974</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>44693</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21979,7 +21979,7 @@
         <v>44920</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>46087</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>45324</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45037</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>45251</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45937</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>45937</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>44986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45057</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22641,7 +22641,7 @@
         <v>46097</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45142</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45218</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22860,7 +22860,7 @@
         <v>45085</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22933,7 +22933,7 @@
         <v>45945</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44756</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>45945</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23152,7 +23152,7 @@
         <v>45945</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>44638</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46106</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45586</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>45954</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44619</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45009</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45279</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23814,7 +23814,7 @@
         <v>44967</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45958</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45350</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45309</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45316</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>44700</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45958</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45958</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>46113</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>46113</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>46113</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>46113</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>45957</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24763,7 +24763,7 @@
         <v>46113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24836,7 +24836,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24909,7 +24909,7 @@
         <v>46112</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46113</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25128,7 +25128,7 @@
         <v>46113</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>46113</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45958</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25347,7 +25347,7 @@
         <v>45092</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>45308</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25493,7 +25493,7 @@
         <v>45961</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45961</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45961</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25712,7 +25712,7 @@
         <v>45107</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45079</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45938</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>46125</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45604</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45266</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44757</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45117</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45972</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>44936</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>45055</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45062</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45537</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>45142</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45783</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45631</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45917</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45178</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45894</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45911</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27318,7 +27318,7 @@
         <v>45923</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27391,7 +27391,7 @@
         <v>45985</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45685</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45784</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         <v>45846</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45846</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>45827</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45968</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45784</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45915</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>45884</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44747</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45664</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44474</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44820</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45880</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45554</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>45028</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28715,7 +28715,7 @@
         <v>45148</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>44988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>44840</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28934,7 +28934,7 @@
         <v>44516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29007,7 +29007,7 @@
         <v>45188</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>45027</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45784</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>45113</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>45204</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>46007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>46007</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44930</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>44748</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45215</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45789</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45238</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>44890</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45743</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30029,7 +30029,7 @@
         <v>44530</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45080</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45043</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>45576</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
         <v>45075</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         <v>45826</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30467,7 +30467,7 @@
         <v>45077</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30540,7 +30540,7 @@
         <v>45537</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>45166</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45012</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>44636</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>45553</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>45532</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30978,7 +30978,7 @@
         <v>45735</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31051,7 +31051,7 @@
         <v>45113</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45264</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>44860</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45234</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45085</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>45538</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45538</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>46148</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>45091</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>46150</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45812</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45541</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31927,7 +31927,7 @@
         <v>45400</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45406</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>46097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32146,7 +32146,7 @@
         <v>45013</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>44609</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45092</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44847</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45133</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>46077</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>45256</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45105</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32735,7 +32735,7 @@
         <v>45832</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45809</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>46158</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32954,7 +32954,7 @@
         <v>46058</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33027,7 +33027,7 @@
         <v>45809</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>46158</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>46158</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>46125</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33319,7 +33319,7 @@
         <v>46158</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33392,7 +33392,7 @@
         <v>46158</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>46158</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33538,7 +33538,7 @@
         <v>45106</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45699</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>46037</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45093</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45108</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45839</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45013</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45711</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45050</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46162</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46162</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>46162</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45695</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34487,7 +34487,7 @@
         <v>44837</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45245</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>46164</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34706,7 +34706,7 @@
         <v>45812</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34779,7 +34779,7 @@
         <v>44545</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34852,7 +34852,7 @@
         <v>46164</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34925,7 +34925,7 @@
         <v>46164</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34998,7 +34998,7 @@
         <v>45344</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
         <v>44551</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35144,7 +35144,7 @@
         <v>45106</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>45393</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>46167</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45387</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45551</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45107</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>46169</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>45107</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45469</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>44628</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45107</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45002</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45602</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36093,7 +36093,7 @@
         <v>45602</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45789</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45133</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45577</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44879</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36458,7 +36458,7 @@
         <v>45020</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45537</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>46177</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>46176</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36750,7 +36750,7 @@
         <v>45156</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36823,7 +36823,7 @@
         <v>45394</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>46177</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36969,7 +36969,7 @@
         <v>46176</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45531</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37115,7 +37115,7 @@
         <v>45035</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45035</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44981</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>45014</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45524</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46181</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37626,7 +37626,7 @@
         <v>45084</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45106</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45573</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45127</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45415</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>46181</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>44512</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45048</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>46183</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45076</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38356,7 +38356,7 @@
         <v>45174</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38429,7 +38429,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>46185</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38575,7 +38575,7 @@
         <v>45170</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45278</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>46188</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38794,7 +38794,7 @@
         <v>45181</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44581</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45749</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>46188</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>45873</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45335</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45334</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>44511</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45875</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45875</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>45610</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45028</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>44596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>46177</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39821,7 +39821,7 @@
         <v>45218</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39894,7 +39894,7 @@
         <v>46199</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>45673</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>46199</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40113,7 +40113,7 @@
         <v>46199</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40186,7 +40186,7 @@
         <v>45218</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40259,7 +40259,7 @@
         <v>44553</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>45075</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>44641</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>44523</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45328</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>44624</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40697,7 +40697,7 @@
         <v>45747</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>45162</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40843,7 +40843,7 @@
         <v>45315</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40916,7 +40916,7 @@
         <v>44619</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40989,7 +40989,7 @@
         <v>44799</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41062,7 +41062,7 @@
         <v>45610</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41135,7 +41135,7 @@
         <v>45883</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>45883</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41281,7 +41281,7 @@
         <v>44636</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45366</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41427,7 +41427,7 @@
         <v>45092</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>44586</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45168</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>45170</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45194</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41792,7 +41792,7 @@
         <v>45095</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45643</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41938,7 +41938,7 @@
         <v>44754</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>46206</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>46206</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45062</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45196</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45090</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>46253</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>46253</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>45198</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44725</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>44706</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45707</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42814,7 +42814,7 @@
         <v>46254</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42887,7 +42887,7 @@
         <v>45761</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42960,7 +42960,7 @@
         <v>46258</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43033,7 +43033,7 @@
         <v>45210</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43106,7 +43106,7 @@
         <v>46254</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>45775</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43252,7 +43252,7 @@
         <v>45531</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43325,7 +43325,7 @@
         <v>45578</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>46258</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43471,7 +43471,7 @@
         <v>45166</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>45173</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>44616</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43690,7 +43690,7 @@
         <v>46177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44728</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45838</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43909,7 +43909,7 @@
         <v>45697</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44742</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44055,7 +44055,7 @@
         <v>44809</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>44711</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46070</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>44757</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>44631</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44420,7 +44420,7 @@
         <v>45463</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44493,7 +44493,7 @@
         <v>45463</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>46265</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>45238</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44712,7 +44712,7 @@
         <v>45180</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>44820</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>46188</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44931,7 +44931,7 @@
         <v>46267</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45004,7 +45004,7 @@
         <v>44722</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45309</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>46268</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45296,7 +45296,7 @@
         <v>44930</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45369,7 +45369,7 @@
         <v>45365</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45630</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>46111</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>46270</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45734,7 +45734,7 @@
         <v>46272</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45361</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45880,7 +45880,7 @@
         <v>44862</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>44886</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>46265</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46099,7 +46099,7 @@
         <v>46274</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46172,7 +46172,7 @@
         <v>44946</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46245,7 +46245,7 @@
         <v>45348</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46318,7 +46318,7 @@
         <v>44851</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46391,7 +46391,7 @@
         <v>44753</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46464,7 +46464,7 @@
         <v>46230</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45309</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46610,7 +46610,7 @@
         <v>45278</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45159</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>44874</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46829,7 +46829,7 @@
         <v>45166</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>46280</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44672</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47048,7 +47048,7 @@
         <v>44636</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44585</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45140</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47267,7 +47267,7 @@
         <v>45070</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45645</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47413,7 +47413,7 @@
         <v>45301</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45335</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45215</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47632,7 +47632,7 @@
         <v>45089</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47705,7 +47705,7 @@
         <v>45981</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47778,7 +47778,7 @@
         <v>44893</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>46112</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47924,7 +47924,7 @@
         <v>44517</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47997,7 +47997,7 @@
         <v>45727</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48070,7 +48070,7 @@
         <v>45495</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45092</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48216,7 +48216,7 @@
         <v>45887</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>46283</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45013</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48435,7 +48435,7 @@
         <v>45610</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48508,7 +48508,7 @@
         <v>46182</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45351</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45092</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46069</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48800,7 +48800,7 @@
         <v>45456</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48873,7 +48873,7 @@
         <v>45001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>44543</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49019,7 +49019,7 @@
         <v>46239</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45238</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45495</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49238,7 +49238,7 @@
         <v>45161</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49311,7 +49311,7 @@
         <v>45243</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45202</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49457,7 +49457,7 @@
         <v>44603</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49530,7 +49530,7 @@
         <v>45358</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45344</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49676,7 +49676,7 @@
         <v>44491</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49749,7 +49749,7 @@
         <v>45162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49822,7 +49822,7 @@
         <v>45783</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>46275</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45923</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>46241</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50143,7 +50143,7 @@
         <v>46283</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50216,7 +50216,7 @@
         <v>45393</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50289,7 +50289,7 @@
         <v>45362</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50362,7 +50362,7 @@
         <v>45887</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>44869</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>44967</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50581,7 +50581,7 @@
         <v>45735</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>45754</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50727,7 +50727,7 @@
         <v>44909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45180</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50873,7 +50873,7 @@
         <v>45182</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50946,7 +50946,7 @@
         <v>45737</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>46241</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46000</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45971</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45019</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45069</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>45093</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46288</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45183</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46245</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>46287</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>44691</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51822,7 +51822,7 @@
         <v>45075</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46209</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51968,7 +51968,7 @@
         <v>46209</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52041,7 +52041,7 @@
         <v>46246</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52114,7 +52114,7 @@
         <v>45579</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52187,7 +52187,7 @@
         <v>46246</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52260,7 +52260,7 @@
         <v>45002</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>45169</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52479,7 +52479,7 @@
         <v>46246</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52552,7 +52552,7 @@
         <v>44741</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52625,7 +52625,7 @@
         <v>46290</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52698,7 +52698,7 @@
         <v>44937</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>45217</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>44580</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>46246</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>45981</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45166</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45035</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>45013</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>45013</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>45225</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>46290</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53647,7 +53647,7 @@
         <v>44930</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45568</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53793,7 +53793,7 @@
         <v>45531</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>44960</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53939,7 +53939,7 @@
         <v>45580</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45104</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>44942</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>45051</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>44593</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54304,7 +54304,7 @@
         <v>45154</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>44875</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>44914</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>45106</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45615</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>45537</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54742,7 +54742,7 @@
         <v>44900</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54815,7 +54815,7 @@
         <v>45195</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>44998</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54961,7 +54961,7 @@
         <v>45324</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
         <v>44592</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55112,7 +55112,7 @@
         <v>45012</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45166</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55258,7 +55258,7 @@
         <v>45085</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55331,7 +55331,7 @@
         <v>45340</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55404,7 +55404,7 @@
         <v>45159</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45048</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>44903</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45370</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>45674</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45454</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>44991</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55915,7 +55915,7 @@
         <v>45028</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55988,7 +55988,7 @@
         <v>45551</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56061,7 +56061,7 @@
         <v>45168</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>45672</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56207,7 +56207,7 @@
         <v>45537</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45254</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56353,7 +56353,7 @@
         <v>45174</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>45662</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45251</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45223</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45094</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45212</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45619</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>45707</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45443</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57010,7 +57010,7 @@
         <v>45328</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57083,7 +57083,7 @@
         <v>45034</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57156,7 +57156,7 @@
         <v>45218</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>45393</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57302,7 +57302,7 @@
         <v>45154</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57375,7 +57375,7 @@
         <v>44545</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57448,7 +57448,7 @@
         <v>45106</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57521,7 +57521,7 @@
         <v>45085</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57594,7 +57594,7 @@
         <v>45085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57667,7 +57667,7 @@
         <v>45082</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57740,7 +57740,7 @@
         <v>45483</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57813,7 +57813,7 @@
         <v>45118</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>45571</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57959,7 +57959,7 @@
         <v>45007</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>45727</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45315</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58178,7 +58178,7 @@
         <v>45631</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>45250</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58324,7 +58324,7 @@
         <v>45698</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58397,7 +58397,7 @@
         <v>45194</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58470,7 +58470,7 @@
         <v>45695</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>45600</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58616,7 +58616,7 @@
         <v>45342</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58689,7 +58689,7 @@
         <v>45165</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58762,7 +58762,7 @@
         <v>45225</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>45075</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>45538</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>45604</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45621</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>45555</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>45075</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45344</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59351,7 +59351,7 @@
         <v>45372</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59424,7 +59424,7 @@
         <v>45499</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59497,7 +59497,7 @@
         <v>45594</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59570,7 +59570,7 @@
         <v>45573</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>45387</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45783</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>45540</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45384</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45624</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45714</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45631</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45691</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45532</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45453</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>45785</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>45656</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45674</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60592,7 +60592,7 @@
         <v>44496</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60665,7 +60665,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>44110</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>43938</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>44825</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60972,7 +60972,7 @@
         <v>45188</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61045,7 +61045,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45373</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61191,7 +61191,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61337,7 +61337,7 @@
         <v>45611</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61410,7 +61410,7 @@
         <v>45271</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61483,7 +61483,7 @@
         <v>45474</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61556,7 +61556,7 @@
         <v>45646</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61629,7 +61629,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61702,7 +61702,7 @@
         <v>45702</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61775,7 +61775,7 @@
         <v>45719</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61848,7 +61848,7 @@
         <v>45734</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61921,7 +61921,7 @@
         <v>45460</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61994,7 +61994,7 @@
         <v>46064</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62067,7 +62067,7 @@
         <v>46070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>46097</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62213,7 +62213,7 @@
         <v>46099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62286,7 +62286,7 @@
         <v>46099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62359,7 +62359,7 @@
         <v>46105</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46164</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62505,7 +62505,7 @@
         <v>46260</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62578,7 +62578,7 @@
         <v>44972</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62651,7 +62651,7 @@
         <v>44960</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45250</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>44981</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62870,7 +62870,7 @@
         <v>46045</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>46196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>45475</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45004</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45961</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45903</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45561</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45905</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46142</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45012</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46188</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45050</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45387</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46069</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45631</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45337</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>46283</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45579</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46251</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45625</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44959</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45474</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45611</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>46099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46101</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45050</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44572</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44585</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44687</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44483</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44676</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44502</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44874</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>44599</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44476</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44719</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44634</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44847</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>44540</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44524</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>44475</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44809</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44480</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44837</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44706</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44579</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44494</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44687</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44596</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44592</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44657</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45400</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45035</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45674</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45315</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45387</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44998</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45393</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45079</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45531</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45643</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>44747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44860</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44890</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44875</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45257</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44672</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45458</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45051</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45215</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44937</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44741</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44491</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44939</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45166</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45034</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44553</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45159</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45142</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45028</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44692</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44545</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45631</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44847</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45785</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44496</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45656</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45453</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45532</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45384</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45266</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45020</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44592</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45315</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44619</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45028</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44691</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45328</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44706</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45743</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45483</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>46027</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44757</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45324</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44930</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44851</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>44593</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45707</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45107</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45846</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46042</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>44747</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45234</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45541</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>46042</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45797</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45797</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45028</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45028</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45693</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44988</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44584</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45770</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45168</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>46051</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45632</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45012</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45393</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>46051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46051</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>46052</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45917</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45923</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45923</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45365</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45925</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45537</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46056</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44512</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45085</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45443</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45930</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45475</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45278</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>44587</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45553</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46066</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45610</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45742</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45532</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45532</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45218</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44974</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45600</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45245</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45204</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45532</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>46056</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45218</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45254</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45537</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45954</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45957</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45958</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46087</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45411</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45697</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45961</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44609</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44609</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44825</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45961</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44586</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45961</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>44820</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45225</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45309</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44516</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>46097</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45972</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45308</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45512</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45443</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45537</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46106</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>44523</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44638</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45013</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45013</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45361</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46112</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>46113</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>46113</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46113</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45846</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>44636</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45826</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45342</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45707</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45846</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45095</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45554</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45526</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44860</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45812</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45050</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45104</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45251</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45316</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45715</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45250</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45084</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44474</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45335</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45915</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45911</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45839</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45334</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45783</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45711</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45370</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45256</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45169</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45251</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44551</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45334</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45812</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45695</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45576</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45784</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45133</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44874</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45180</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45923</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45166</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45166</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45210</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45647</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45415</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45968</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45091</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45156</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45917</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45664</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45012</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45884</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45159</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45980</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45728</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45784</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45784</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45350</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45035</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45789</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44742</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45343</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45106</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>44628</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45089</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44636</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45602</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45602</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45789</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45645</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45580</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45217</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45713</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45212</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45645</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45749</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45173</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45873</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45579</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45340</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44911</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45013</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45538</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45727</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45407</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45735</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46148</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46150</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45118</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45106</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45002</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44936</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44753</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45194</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44862</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45630</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46097</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45832</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45133</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46077</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45551</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45117</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45809</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45168</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45351</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>46125</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45875</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>46158</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45699</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45809</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>46158</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46158</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46158</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>46158</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>46158</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45875</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46037</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45619</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46058</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46162</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44530</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44837</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>44473</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45537</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>46164</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46167</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45012</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>46164</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46164</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44809</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45077</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46169</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44942</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45604</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44728</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39205,7 +39205,7 @@
         <v>45695</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45469</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45883</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45883</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>44981</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45610</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>46176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>46176</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45749</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45610</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>44876</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45551</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45127</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46181</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46182</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46181</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45512</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45166</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>46183</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44543</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45261</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>46188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>46185</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45366</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45075</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>44930</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45013</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45082</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45014</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45085</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44614</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45007</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45007</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46177</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45551</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44691</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>46199</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>46199</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>46199</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45085</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>44799</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44641</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>45537</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45538</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45170</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45166</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44631</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45463</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45463</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46206</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45057</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44754</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45092</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>46206</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45009</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45455</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45838</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45238</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44511</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46258</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44580</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46258</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45315</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46070</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45113</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>44881</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44920</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46265</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45055</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>46267</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46268</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44988</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46269</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>44960</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>46230</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45387</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>46270</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46272</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45080</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46111</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45247</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46274</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45105</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45499</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45165</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>46280</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45524</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45218</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44866</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45264</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45188</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45093</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>46283</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45113</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>46241</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45321</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45727</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45887</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45981</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46283</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45735</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45754</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45887</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45127</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45393</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45456</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45495</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45334</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>46239</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44869</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45662</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45923</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45202</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>45019</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>44909</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45093</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45737</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>45971</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45531</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45362</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45243</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45358</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45001</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45238</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>44991</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>44624</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>44939</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>44939</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45393</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45180</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45278</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45783</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45344</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46275</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45069</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45092</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>46241</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45204</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45013</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45162</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45161</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>45495</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>46069</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>46112</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>46000</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44967</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45698</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44585</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>46246</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>46246</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>46246</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>44893</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45394</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>46209</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52160,7 +52160,7 @@
         <v>46209</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45344</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>46246</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>46245</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44820</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45673</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>46288</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45309</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45142</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>46246</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>44840</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46290</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45577</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45094</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45208</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45531</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>45981</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>46290</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46290</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45140</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46290</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45524</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>46265</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45218</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>44757</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>44619</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45195</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>45180</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>46294</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>45637</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>45181</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>44825</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>46294</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>45309</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45747</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>46294</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>45090</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>45324</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45223</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>46254</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45170</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45042</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45406</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45162</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44893</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45092</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>46297</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46049</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>46294</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>46254</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>44930</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>45092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45454</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>45169</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45573</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45761</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>44517</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>45027</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>45194</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45309</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>44700</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45674</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>45183</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>44603</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>45225</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45393</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>44616</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45174</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45070</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45037</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45092</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45076</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>44900</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45266</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45571</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45565</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>44722</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>44903</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45154</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>44711</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>44693</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>44581</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45075</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45616</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>45062</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45113</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45672</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45301</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45030</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>45348</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>44748</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59095,7 +59095,7 @@
         <v>45775</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>45028</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>45075</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45604</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45075</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45538</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45594</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45555</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45344</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45499</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59903,7 +59903,7 @@
         <v>45372</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45573</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>45621</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45783</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45387</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45624</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45674</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>45714</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>44825</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>43938</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>44110</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>44831</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45188</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>44959</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>45373</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>45155</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>45611</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>45271</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>45474</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61378,7 +61378,7 @@
         <v>45646</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>45734</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45702</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45719</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45734</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>45460</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61816,7 +61816,7 @@
         <v>46064</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61889,7 +61889,7 @@
         <v>46070</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
         <v>46097</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62035,7 +62035,7 @@
         <v>46099</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>46099</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>46105</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62254,7 +62254,7 @@
         <v>46164</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62327,7 +62327,7 @@
         <v>46260</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>44972</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62473,7 +62473,7 @@
         <v>44960</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         <v>45250</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62619,7 +62619,7 @@
         <v>44981</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46045</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46119</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>46196</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2118,7 +2118,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>45475</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>46182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>44960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45901</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>45089</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>45004</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>45303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>45961</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>46112</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45903</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>45561</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46070</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>46125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45905</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45917</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>45847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>46142</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>45012</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>46188</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45050</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45387</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         <v>46069</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>45110</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>45631</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>45337</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>46283</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>45579</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>46251</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45085</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45625</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44959</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7870,7 +7870,7 @@
         <v>45474</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>45611</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>46064</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>46099</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>46101</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>45050</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44572</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44585</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44687</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44483</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44691</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44676</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44502</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>44497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10179,7 +10179,7 @@
         <v>44624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44629</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44874</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44501</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>44572</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10617,7 +10617,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>44599</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44491</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>44588</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>44476</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10982,7 +10982,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>44484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44719</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>44825</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44634</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44847</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
         <v>44540</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>44524</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>44475</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44809</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44621</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44859</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44743</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44742</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44480</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44837</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44706</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44579</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44494</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44687</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44596</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44592</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44608</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44711</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44657</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>44858</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>44875</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>45400</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45035</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45674</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45315</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>45387</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>44998</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44886</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45393</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14204,7 +14204,7 @@
         <v>45079</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>45531</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45643</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>44747</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44860</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>44890</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45373</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44875</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45257</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44672</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45458</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45051</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45215</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>44937</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>44741</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         <v>45196</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44491</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>44946</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15591,7 +15591,7 @@
         <v>44967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         <v>44939</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45166</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45034</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>44553</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>45159</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45578</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45142</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16248,7 +16248,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16321,7 +16321,7 @@
         <v>45002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45028</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16467,7 +16467,7 @@
         <v>44692</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16540,7 +16540,7 @@
         <v>44545</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16613,7 +16613,7 @@
         <v>45631</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16686,7 +16686,7 @@
         <v>44847</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45785</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16832,7 +16832,7 @@
         <v>45198</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44496</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45656</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>45453</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45532</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>45384</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45075</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45266</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45020</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>44592</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45315</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44879</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45540</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>44619</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45028</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>46007</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>46007</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45586</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44691</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45328</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44706</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45743</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45483</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>46027</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>45335</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44757</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45324</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>44930</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18954,7 +18954,7 @@
         <v>44851</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>44593</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45707</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45107</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>45846</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>45908</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>46042</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>44747</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45234</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>45541</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19757,7 +19757,7 @@
         <v>46042</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19830,7 +19830,7 @@
         <v>46042</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45797</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19976,7 +19976,7 @@
         <v>45797</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45796</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>44636</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20268,7 +20268,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>45028</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         <v>46055</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45028</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45693</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45581</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44988</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>44584</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45770</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20925,7 +20925,7 @@
         <v>45168</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20998,7 +20998,7 @@
         <v>45918</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>46051</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45632</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>44592</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45012</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45393</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>46051</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46051</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>46052</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21655,7 +21655,7 @@
         <v>45917</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21728,7 +21728,7 @@
         <v>45923</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21801,7 +21801,7 @@
         <v>45923</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
         <v>45365</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45747</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45925</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45537</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>45929</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>46056</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45929</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44512</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45085</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45443</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45930</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
         <v>45475</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45278</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>44587</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45553</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46066</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45610</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45742</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45532</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45532</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45218</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45945</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45945</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45945</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44974</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45600</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45245</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45204</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>45532</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>46056</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45218</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45254</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45537</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45954</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45957</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45958</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24575,7 +24575,7 @@
         <v>45958</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24648,7 +24648,7 @@
         <v>45958</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24721,7 +24721,7 @@
         <v>46087</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45958</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45958</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45958</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45411</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>45697</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>45961</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>44609</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44609</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>44825</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25612,7 +25612,7 @@
         <v>45085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45961</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>44586</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45961</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>44820</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45938</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>44725</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>45225</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45309</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>44516</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>46097</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45972</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45308</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>45512</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45443</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45537</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46106</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>44523</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27077,7 +27077,7 @@
         <v>44638</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45013</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45013</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45361</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>46112</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>46113</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>46113</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>46113</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>46113</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>46113</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46113</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46113</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45162</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>45846</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>44636</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45826</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>45342</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45707</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28469,7 +28469,7 @@
         <v>45846</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45095</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45554</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45526</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>44860</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45812</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>45050</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45104</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45251</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45316</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45715</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29277,7 +29277,7 @@
         <v>45250</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>45084</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>44474</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29496,7 +29496,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29569,7 +29569,7 @@
         <v>45335</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45915</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45911</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29788,7 +29788,7 @@
         <v>45839</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29861,7 +29861,7 @@
         <v>45334</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29934,7 +29934,7 @@
         <v>45783</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45711</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>45985</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45370</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45256</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>45169</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30372,7 +30372,7 @@
         <v>45251</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>44551</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>45685</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45334</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45812</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>45695</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>45576</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45784</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45133</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44874</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45894</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45880</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45180</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45923</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45166</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45166</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45210</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45647</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>45415</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45968</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45091</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45156</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45917</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45664</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45012</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45884</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45159</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45980</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45728</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45784</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45784</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>45350</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45035</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45035</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45789</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>44742</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45343</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45106</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>44628</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45089</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>44636</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45602</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45602</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45148</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45789</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45106</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45645</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45580</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45217</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45713</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45212</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45631</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45645</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45749</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45173</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45873</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45579</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45340</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>44911</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45013</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45538</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45727</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45407</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>45735</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>46148</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>46150</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45118</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45106</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>45002</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>44936</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>44753</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45194</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>44862</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45106</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35920,7 +35920,7 @@
         <v>45630</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>46097</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45832</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45133</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36212,7 +36212,7 @@
         <v>46077</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
         <v>45551</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36358,7 +36358,7 @@
         <v>45117</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36431,7 +36431,7 @@
         <v>45809</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>45168</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36577,7 +36577,7 @@
         <v>45351</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36650,7 +36650,7 @@
         <v>46125</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>45875</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>46158</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45699</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45809</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>46158</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>46158</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>46158</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>46158</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>46158</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45875</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46037</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45619</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45154</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>46058</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46162</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44530</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44837</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>44473</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46162</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>45537</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>46164</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38329,7 +38329,7 @@
         <v>46167</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45012</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>46164</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46164</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>44809</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>44756</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45077</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>46169</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>44942</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38986,7 +38986,7 @@
         <v>45604</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45107</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44728</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39205,7 +39205,7 @@
         <v>45695</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45469</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45883</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39424,7 +39424,7 @@
         <v>45883</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39497,7 +39497,7 @@
         <v>44981</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45610</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39643,7 +39643,7 @@
         <v>44596</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>46176</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
         <v>46176</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45749</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>46177</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40013,7 +40013,7 @@
         <v>45610</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>44876</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>45551</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>46177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40305,7 +40305,7 @@
         <v>45127</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>46181</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46182</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>46181</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45512</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40743,7 +40743,7 @@
         <v>45166</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40816,7 +40816,7 @@
         <v>46183</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>44543</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>45261</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46188</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>46188</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41181,7 +41181,7 @@
         <v>46185</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41254,7 +41254,7 @@
         <v>45366</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45075</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41400,7 +41400,7 @@
         <v>44930</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45013</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45082</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41619,7 +41619,7 @@
         <v>45014</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41692,7 +41692,7 @@
         <v>45085</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41765,7 +41765,7 @@
         <v>45107</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>44614</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>45007</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45007</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>46177</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>45215</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45551</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44691</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42349,7 +42349,7 @@
         <v>46199</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>46199</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>46199</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42568,7 +42568,7 @@
         <v>45085</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>44799</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42714,7 +42714,7 @@
         <v>44641</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42787,7 +42787,7 @@
         <v>45077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>45537</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45538</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43006,7 +43006,7 @@
         <v>45170</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43079,7 +43079,7 @@
         <v>45166</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43152,7 +43152,7 @@
         <v>45251</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43225,7 +43225,7 @@
         <v>44631</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45463</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45463</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46206</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>45057</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43590,7 +43590,7 @@
         <v>44754</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43663,7 +43663,7 @@
         <v>45092</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43736,7 +43736,7 @@
         <v>46206</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43809,7 +43809,7 @@
         <v>45009</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>46177</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43955,7 +43955,7 @@
         <v>45455</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44028,7 +44028,7 @@
         <v>45838</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45238</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>44511</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>46258</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>44580</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>46258</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45315</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44539,7 +44539,7 @@
         <v>45043</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44612,7 +44612,7 @@
         <v>46070</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45113</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>44881</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44831,7 +44831,7 @@
         <v>44920</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>46265</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45055</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>46188</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>46267</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46268</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>44545</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46268</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>44988</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46269</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>44960</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>46230</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45279</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>45387</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>46270</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46272</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>45080</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>46111</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45247</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46218,7 +46218,7 @@
         <v>46274</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46291,7 +46291,7 @@
         <v>45105</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45106</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>45499</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45165</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>46280</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>45524</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>45218</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>44866</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45264</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45188</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45093</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>46283</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>45113</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>46241</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>45321</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45727</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>45887</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47605,7 +47605,7 @@
         <v>45981</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>46283</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47751,7 +47751,7 @@
         <v>45735</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47824,7 +47824,7 @@
         <v>45754</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47897,7 +47897,7 @@
         <v>45887</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47970,7 +47970,7 @@
         <v>45127</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45393</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>45238</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48189,7 +48189,7 @@
         <v>45456</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48262,7 +48262,7 @@
         <v>45495</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48335,7 +48335,7 @@
         <v>45334</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48408,7 +48408,7 @@
         <v>46239</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45092</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>44869</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48627,7 +48627,7 @@
         <v>45662</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>45923</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48773,7 +48773,7 @@
         <v>45202</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48846,7 +48846,7 @@
         <v>45019</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>44909</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
         <v>45093</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49065,7 +49065,7 @@
         <v>45182</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49138,7 +49138,7 @@
         <v>45737</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49211,7 +49211,7 @@
         <v>45971</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45531</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49357,7 +49357,7 @@
         <v>45362</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49430,7 +49430,7 @@
         <v>45243</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45358</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49576,7 +49576,7 @@
         <v>45001</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49649,7 +49649,7 @@
         <v>46287</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45238</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>44991</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>44624</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>44939</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>44939</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45393</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45180</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50233,7 +50233,7 @@
         <v>45278</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50306,7 +50306,7 @@
         <v>45783</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50379,7 +50379,7 @@
         <v>45344</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50452,7 +50452,7 @@
         <v>46275</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50554,7 +50554,7 @@
         <v>45069</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45092</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>46241</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>45204</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50846,7 +50846,7 @@
         <v>45013</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45162</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50992,7 +50992,7 @@
         <v>45161</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51065,7 +51065,7 @@
         <v>45495</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51138,7 +51138,7 @@
         <v>46069</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51211,7 +51211,7 @@
         <v>46112</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51284,7 +51284,7 @@
         <v>46000</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51357,7 +51357,7 @@
         <v>44967</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45698</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>45178</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44585</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>46246</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>46246</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51795,7 +51795,7 @@
         <v>46246</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>45062</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>44893</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>45394</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52087,7 +52087,7 @@
         <v>46209</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52160,7 +52160,7 @@
         <v>46209</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45344</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52306,7 +52306,7 @@
         <v>46246</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>46245</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52452,7 +52452,7 @@
         <v>44820</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45673</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>46288</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52671,7 +52671,7 @@
         <v>45309</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52744,7 +52744,7 @@
         <v>45142</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>46246</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52890,7 +52890,7 @@
         <v>44840</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52963,7 +52963,7 @@
         <v>46290</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53036,7 +53036,7 @@
         <v>45577</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45094</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53182,7 +53182,7 @@
         <v>45208</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53255,7 +53255,7 @@
         <v>45531</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>45981</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53401,7 +53401,7 @@
         <v>46290</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>46290</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45140</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>46290</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53693,7 +53693,7 @@
         <v>45524</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>46265</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45218</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>44757</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>44619</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45195</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54131,7 +54131,7 @@
         <v>45180</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54204,7 +54204,7 @@
         <v>46294</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54277,7 +54277,7 @@
         <v>45637</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>46182</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54423,7 +54423,7 @@
         <v>45181</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>44825</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54569,7 +54569,7 @@
         <v>46294</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54642,7 +54642,7 @@
         <v>45309</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>45747</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54788,7 +54788,7 @@
         <v>46294</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54861,7 +54861,7 @@
         <v>45090</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54934,7 +54934,7 @@
         <v>45324</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45223</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55080,7 +55080,7 @@
         <v>46254</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55153,7 +55153,7 @@
         <v>45170</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>45042</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45406</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>45162</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>44893</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>46253</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>46297</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>46253</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45092</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>46297</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>46049</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55956,7 +55956,7 @@
         <v>46294</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56029,7 +56029,7 @@
         <v>46254</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56102,7 +56102,7 @@
         <v>44930</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56175,7 +56175,7 @@
         <v>45092</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45454</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56321,7 +56321,7 @@
         <v>45169</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45573</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>45761</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56540,7 +56540,7 @@
         <v>44517</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56613,7 +56613,7 @@
         <v>45027</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>45194</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56759,7 +56759,7 @@
         <v>45309</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56832,7 +56832,7 @@
         <v>44700</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56905,7 +56905,7 @@
         <v>45674</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56978,7 +56978,7 @@
         <v>45183</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>44603</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57124,7 +57124,7 @@
         <v>45225</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57197,7 +57197,7 @@
         <v>45393</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57270,7 +57270,7 @@
         <v>44616</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57343,7 +57343,7 @@
         <v>45174</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>45070</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57489,7 +57489,7 @@
         <v>45037</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57562,7 +57562,7 @@
         <v>45092</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57635,7 +57635,7 @@
         <v>45076</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57708,7 +57708,7 @@
         <v>44900</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57781,7 +57781,7 @@
         <v>45266</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
         <v>45571</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57927,7 +57927,7 @@
         <v>45565</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58000,7 +58000,7 @@
         <v>44722</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58073,7 +58073,7 @@
         <v>44903</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45154</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58219,7 +58219,7 @@
         <v>44711</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>44693</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>44581</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45075</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45616</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>45062</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45113</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45672</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58803,7 +58803,7 @@
         <v>45301</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58876,7 +58876,7 @@
         <v>45030</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58949,7 +58949,7 @@
         <v>45348</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59022,7 +59022,7 @@
         <v>44748</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59095,7 +59095,7 @@
         <v>45775</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45048</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59241,7 +59241,7 @@
         <v>45028</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>45075</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59387,7 +59387,7 @@
         <v>45604</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59460,7 +59460,7 @@
         <v>45075</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59533,7 +59533,7 @@
         <v>45538</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59606,7 +59606,7 @@
         <v>45594</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59679,7 +59679,7 @@
         <v>45555</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59752,7 +59752,7 @@
         <v>45344</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45499</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59903,7 +59903,7 @@
         <v>45372</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59976,7 +59976,7 @@
         <v>45573</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60049,7 +60049,7 @@
         <v>45621</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60122,7 +60122,7 @@
         <v>45783</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60195,7 +60195,7 @@
         <v>45387</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60268,7 +60268,7 @@
         <v>45624</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60341,7 +60341,7 @@
         <v>45674</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>45714</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>44825</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60565,7 +60565,7 @@
         <v>43938</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>44110</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>44831</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45188</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60867,7 +60867,7 @@
         <v>44959</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60940,7 +60940,7 @@
         <v>45373</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61013,7 +61013,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61086,7 +61086,7 @@
         <v>45155</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61159,7 +61159,7 @@
         <v>45611</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61232,7 +61232,7 @@
         <v>45271</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61305,7 +61305,7 @@
         <v>45474</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61378,7 +61378,7 @@
         <v>45646</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61451,7 +61451,7 @@
         <v>45734</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61524,7 +61524,7 @@
         <v>45702</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61597,7 +61597,7 @@
         <v>45719</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>45734</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>45460</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61816,7 +61816,7 @@
         <v>46064</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61889,7 +61889,7 @@
         <v>46070</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61962,7 +61962,7 @@
         <v>46097</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62035,7 +62035,7 @@
         <v>46099</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62108,7 +62108,7 @@
         <v>46099</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62181,7 +62181,7 @@
         <v>46105</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62254,7 +62254,7 @@
         <v>46164</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62327,7 +62327,7 @@
         <v>46260</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62400,7 +62400,7 @@
         <v>44972</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62473,7 +62473,7 @@
         <v>44960</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62546,7 +62546,7 @@
         <v>45250</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62619,7 +62619,7 @@
         <v>44981</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         <v>46045</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45475</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>46182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45901</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45085</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45103</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45387</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45625</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>45050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45631</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45050</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>45012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45561</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>45004</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>46112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46125</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>46142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46280</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>46069</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45337</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>46283</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44483</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44687</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44659</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44719</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44588</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44540</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>44596</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44623</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44809</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44484</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44592</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>44608</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>44719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>44742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44627</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44634</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44608</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44494</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44711</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44881</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45204</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45166</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45091</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44657</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44858</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44875</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45085</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45321</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45541</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45092</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45400</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45013</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45340</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44609</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45159</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45048</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45370</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44847</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45334</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45674</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45713</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45105</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45454</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44991</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45247</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45715</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44825</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45334</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44860</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45106</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45093</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45108</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45013</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45393</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45050</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45411</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45028</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45042</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45387</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44876</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45455</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45532</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45551</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45257</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44866</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45526</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44545</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45672</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45266</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44825</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45537</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45458</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>45254</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45344</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44619</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45662</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45106</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45393</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45387</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45551</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>45251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45883</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45315</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45223</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45443</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45094</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45212</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45619</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45707</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45443</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45328</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45469</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44628</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45309</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45393</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45107</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45154</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44545</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45002</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45082</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45483</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45577</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44879</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45118</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45020</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45571</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45007</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45727</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45315</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45631</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>44939</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45698</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45512</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45030</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45194</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45537</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45695</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45846</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45600</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44609</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45394</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45499</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44893</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45373</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45531</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45524</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44747</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45342</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45035</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45035</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45165</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44981</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45014</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44592</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45647</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45524</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45075</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>45538</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45604</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45621</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45075</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45344</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45372</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45499</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45594</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44584</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45573</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45573</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45674</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45415</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44512</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45048</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45076</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45077</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45174</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44614</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45387</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45645</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45783</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44691</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44587</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45384</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45170</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45278</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45624</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45714</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45631</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45691</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44581</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>45616</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45742</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45532</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45785</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45028</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45028</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45917</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45923</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45335</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45923</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45656</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44692</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45747</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45674</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44496</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44511</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45565</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44911</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45925</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45930</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45929</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45610</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45637</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45028</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45796</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44596</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45218</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45673</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44693</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45169</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45218</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44553</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45075</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44920</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44641</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44523</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45328</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45324</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45037</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45797</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45797</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44624</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45581</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45251</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45162</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45315</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45693</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44799</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45632</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45012</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44636</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44986</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45057</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45366</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44586</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45393</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45218</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45170</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45194</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45095</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44756</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45643</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44754</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45062</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44638</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45937</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45251</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45196</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45586</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44619</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>45198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45945</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45945</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45279</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45945</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44725</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44967</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45350</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45309</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44706</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45316</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44700</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45537</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45210</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45092</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45531</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45578</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45308</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>45166</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45173</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44616</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45079</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45826</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45604</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44757</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44728</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45697</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44742</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44809</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45117</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45954</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45958</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45958</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45957</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45958</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>45958</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45958</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44936</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>44711</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45961</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45062</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45256</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>45961</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45961</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>45938</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44757</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45839</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44631</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45142</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45711</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45631</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45463</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45463</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45178</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45695</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45812</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45238</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45972</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45180</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>44820</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44747</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>44820</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>44722</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45309</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45028</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45365</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45602</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45602</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45148</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45789</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45630</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45978</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44840</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44516</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45188</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45027</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45361</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44862</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45113</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45204</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44886</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45749</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>44930</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44946</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45348</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45873</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>44851</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45875</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>44748</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45875</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>44753</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45309</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45278</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45238</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45159</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44874</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>45166</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46097</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>44890</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>44672</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>44636</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>44585</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44530</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>45140</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>45080</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45070</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45645</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45301</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>45043</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>45075</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45335</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45215</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45537</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45166</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45012</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44636</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45553</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>45532</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45089</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45735</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45113</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45264</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45846</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>45846</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>44893</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>46113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>46113</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>44517</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>46112</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>44860</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46113</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45234</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45610</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>46113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>46113</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45538</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45538</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45351</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44543</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>44603</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>44491</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45554</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45183</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44691</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45075</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45783</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45917</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45579</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45894</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45911</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45923</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45002</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45985</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45169</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>44741</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>46007</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>46007</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>44937</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45685</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45784</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45217</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>44580</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45827</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45968</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45784</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45915</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45884</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45980</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45664</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45166</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45880</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45035</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45013</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45013</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46027</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>44930</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45568</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45531</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>44960</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45784</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45580</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45104</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>44942</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45051</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>46042</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>46042</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>46042</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44593</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45154</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>44875</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>44914</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>45615</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46055</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45537</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>44900</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>45195</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45576</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>44998</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>45324</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>44592</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>45012</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46051</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>46051</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>46051</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>46052</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>46056</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>46066</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>46150</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>46097</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>46056</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45133</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>46077</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>46087</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45832</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45809</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>46158</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>46058</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45809</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>46158</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>46158</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>46125</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>46158</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>46158</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>46158</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45699</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46037</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>46162</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>46162</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>46162</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>44837</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>46164</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>46164</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>46164</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52170,7 +52170,7 @@
         <v>46169</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52243,7 +52243,7 @@
         <v>46176</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>46177</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>46176</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>46181</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>46181</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>46183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>46182</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46185</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46188</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>46188</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46177</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>46199</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46199</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>46199</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>46206</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>46206</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>46177</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45838</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>46070</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>46265</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>46267</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>46268</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>46268</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>46269</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>46270</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>46272</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>46274</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46230</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45981</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46112</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>45727</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45495</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54652,7 +54652,7 @@
         <v>45092</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45887</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>46283</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45013</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45092</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>46069</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45456</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55163,7 +55163,7 @@
         <v>45001</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>46239</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45238</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45495</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>45161</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>45243</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45202</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>45358</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>45344</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>45162</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>45783</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>45923</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46241</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>46283</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45393</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56360,7 +56360,7 @@
         <v>45362</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45887</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>44869</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>44967</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45735</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45754</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>44909</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45180</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45182</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45737</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>46241</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>46000</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45971</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45019</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57382,7 +57382,7 @@
         <v>45069</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45093</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>46245</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>46287</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>46209</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>46209</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>46246</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57966,7 +57966,7 @@
         <v>46246</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58039,7 +58039,7 @@
         <v>46246</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>46246</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>46290</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46246</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45981</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46290</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>46290</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46290</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>46294</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>46294</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>46253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>46182</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>46294</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>46049</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>46297</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>46254</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>46254</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>46302</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>46302</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>46258</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>46258</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59718,7 +59718,7 @@
         <v>46181</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>46304</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>46265</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45761</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>46111</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>46297</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>44831</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>44110</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
         <v>43938</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44825</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45188</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>44959</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45373</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>44959</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45155</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60828,7 +60828,7 @@
         <v>45611</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45271</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>45474</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>45646</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45734</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>45702</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45719</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61339,7 +61339,7 @@
         <v>45734</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45460</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>46064</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61558,7 +61558,7 @@
         <v>46070</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61631,7 +61631,7 @@
         <v>46097</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61704,7 +61704,7 @@
         <v>46099</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61777,7 +61777,7 @@
         <v>46099</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>46105</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>46164</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61996,7 +61996,7 @@
         <v>46260</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>44972</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>44960</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45250</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>44981</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46045</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45474</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         <v>45923</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>45999</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45832</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
         <v>45475</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>46182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         <v>44960</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44930</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>45089</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         <v>45901</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>45393</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>45085</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45103</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45387</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45625</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>45603</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5124,7 +5124,7 @@
         <v>45050</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45631</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45579</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45050</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>45012</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>45561</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>45004</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>45961</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>45303</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>45002</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45903</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>46112</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>46125</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>45917</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>45905</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>46142</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>46188</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>46280</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>46069</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>45337</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>46283</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>46251</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8087,7 +8087,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8685,7 +8685,7 @@
         <v>44551</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8758,7 +8758,7 @@
         <v>44572</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9123,7 +9123,7 @@
         <v>44875</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9269,7 +9269,7 @@
         <v>44483</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44687</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>44559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44526</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44659</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>44629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44719</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>44588</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>44847</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>44480</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>44516</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>44540</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>44596</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11386,7 +11386,7 @@
         <v>44623</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44837</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44524</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44809</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44706</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>44484</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11902,7 +11902,7 @@
         <v>44592</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11980,7 +11980,7 @@
         <v>44608</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12053,7 +12053,7 @@
         <v>44579</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44621</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12199,7 +12199,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         <v>44719</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
         <v>44742</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44743</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
         <v>44627</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44634</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
         <v>44608</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>44825</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44494</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12856,7 +12856,7 @@
         <v>44687</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>44503</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>44711</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>44881</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>44804</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44614</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>45407</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>45204</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13440,7 +13440,7 @@
         <v>45166</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45091</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>44657</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44858</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44875</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45085</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45321</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45541</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45092</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>45400</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45406</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45013</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45340</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44609</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>45092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>45159</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45048</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>44903</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>45370</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>45180</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44847</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>45334</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45674</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45713</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45105</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45454</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44991</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15416,7 +15416,7 @@
         <v>45247</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45715</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45512</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44825</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>45334</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44860</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>45106</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45093</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44847</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>45108</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>45013</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45393</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45050</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45411</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45028</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16511,7 +16511,7 @@
         <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>45042</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16657,7 +16657,7 @@
         <v>45387</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>44876</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16803,7 +16803,7 @@
         <v>45455</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16876,7 +16876,7 @@
         <v>45532</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16949,7 +16949,7 @@
         <v>45532</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>45551</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17168,7 +17168,7 @@
         <v>45257</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>45245</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44866</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>45526</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17460,7 +17460,7 @@
         <v>44545</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17533,7 +17533,7 @@
         <v>45672</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45266</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44825</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>45537</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45458</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>45254</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>45344</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45174</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>44619</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44551</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>45662</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>45106</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>45393</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45387</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45551</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18701,7 +18701,7 @@
         <v>45251</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45107</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45883</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>45883</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45315</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45223</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19139,7 +19139,7 @@
         <v>45127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45443</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45094</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45212</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45619</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45707</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19577,7 +19577,7 @@
         <v>45443</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45328</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19723,7 +19723,7 @@
         <v>45107</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19869,7 +19869,7 @@
         <v>45469</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19942,7 +19942,7 @@
         <v>44628</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>45309</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45393</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45107</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>45749</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45154</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44545</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45106</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20599,7 +20599,7 @@
         <v>45002</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20672,7 +20672,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45082</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
         <v>45113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45483</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45133</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21110,7 +21110,7 @@
         <v>45577</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21183,7 +21183,7 @@
         <v>44879</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45118</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45020</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>45571</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45007</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45727</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21621,7 +21621,7 @@
         <v>45315</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45631</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21767,7 +21767,7 @@
         <v>45250</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>44939</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44939</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21986,7 +21986,7 @@
         <v>45475</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22059,7 +22059,7 @@
         <v>45698</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45512</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22205,7 +22205,7 @@
         <v>45030</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
         <v>45194</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45537</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45695</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>45156</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45846</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45600</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44609</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45394</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45499</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22940,7 +22940,7 @@
         <v>44893</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45373</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>45531</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>45524</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45908</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>44747</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45342</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>45035</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23524,7 +23524,7 @@
         <v>45035</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23597,7 +23597,7 @@
         <v>45165</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23670,7 +23670,7 @@
         <v>44981</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45014</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45225</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44592</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45647</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>45524</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45075</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45162</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24254,7 +24254,7 @@
         <v>45538</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45604</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45621</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>45551</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
         <v>45075</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24692,7 +24692,7 @@
         <v>45344</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45372</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45499</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45594</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>44584</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45573</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45084</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45573</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45674</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45415</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44512</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44988</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45048</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25792,7 +25792,7 @@
         <v>45076</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25865,7 +25865,7 @@
         <v>45077</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45174</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44614</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26084,7 +26084,7 @@
         <v>45387</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45645</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45645</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45783</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45917</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26449,7 +26449,7 @@
         <v>45540</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26522,7 +26522,7 @@
         <v>44691</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26595,7 +26595,7 @@
         <v>44587</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26668,7 +26668,7 @@
         <v>45007</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45384</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26814,7 +26814,7 @@
         <v>45170</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>45278</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45918</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27033,7 +27033,7 @@
         <v>45624</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>45714</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45631</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45691</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>45181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44581</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>45616</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45742</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>45532</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45453</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45785</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44939</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45028</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45028</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45917</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45923</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45335</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45923</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45656</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44692</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45747</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45674</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>44496</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44511</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45565</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>44911</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45261</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45925</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45930</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45929</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45610</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45637</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45028</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45796</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>44596</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45218</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45673</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>44974</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44693</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45169</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45218</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>44553</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45075</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30323,7 +30323,7 @@
         <v>44920</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>44641</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44523</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45328</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>45324</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30688,7 +30688,7 @@
         <v>45037</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45797</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45797</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44624</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>45581</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31053,7 +31053,7 @@
         <v>45770</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45251</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31199,7 +31199,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45162</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45315</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31418,7 +31418,7 @@
         <v>45693</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31491,7 +31491,7 @@
         <v>44799</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45632</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31637,7 +31637,7 @@
         <v>45610</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>45012</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44636</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>44986</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31929,7 +31929,7 @@
         <v>45057</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45366</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45092</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32148,7 +32148,7 @@
         <v>45142</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32221,7 +32221,7 @@
         <v>44586</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>45393</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45218</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32440,7 +32440,7 @@
         <v>45168</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>45170</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32586,7 +32586,7 @@
         <v>45194</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45095</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45085</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44756</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45643</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44754</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45062</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>44638</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45937</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45251</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45196</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45586</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33535,7 +33535,7 @@
         <v>44619</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>45009</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
         <v>45198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45945</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45945</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45279</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45945</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>44725</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>44967</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45350</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45309</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44706</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34411,7 +34411,7 @@
         <v>45316</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44700</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34557,7 +34557,7 @@
         <v>45707</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45537</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34703,7 +34703,7 @@
         <v>45210</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45092</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34849,7 +34849,7 @@
         <v>45775</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>45531</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>45578</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35068,7 +35068,7 @@
         <v>45308</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35141,7 +35141,7 @@
         <v>45107</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35214,7 +35214,7 @@
         <v>45166</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35287,7 +35287,7 @@
         <v>45173</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>44616</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35433,7 +35433,7 @@
         <v>45079</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35506,7 +35506,7 @@
         <v>45826</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45604</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45266</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>44757</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>44728</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45697</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35944,7 +35944,7 @@
         <v>44742</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36017,7 +36017,7 @@
         <v>44809</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36090,7 +36090,7 @@
         <v>45117</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36163,7 +36163,7 @@
         <v>45954</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45958</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36309,7 +36309,7 @@
         <v>45958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45958</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45957</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45958</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36601,7 +36601,7 @@
         <v>45958</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36674,7 +36674,7 @@
         <v>45958</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36747,7 +36747,7 @@
         <v>45812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36820,7 +36820,7 @@
         <v>44936</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>45055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>44711</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45961</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45062</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45256</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>45961</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45961</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>45938</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37477,7 +37477,7 @@
         <v>44757</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37550,7 +37550,7 @@
         <v>45839</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37623,7 +37623,7 @@
         <v>44631</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45142</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37769,7 +37769,7 @@
         <v>45711</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45631</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>45463</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45463</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38061,7 +38061,7 @@
         <v>45178</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38134,7 +38134,7 @@
         <v>45728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38207,7 +38207,7 @@
         <v>45695</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38280,7 +38280,7 @@
         <v>45812</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38353,7 +38353,7 @@
         <v>45238</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38426,7 +38426,7 @@
         <v>45972</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38499,7 +38499,7 @@
         <v>45180</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38572,7 +38572,7 @@
         <v>44820</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44747</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>44820</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>44722</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45309</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45028</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45365</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45602</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45602</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45148</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45789</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45630</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45978</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44840</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44516</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45188</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45027</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>45361</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44862</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45113</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45204</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44886</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45749</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>44930</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44946</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45348</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45873</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>44851</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45875</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>44748</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45875</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>44753</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>45309</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>45278</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45215</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45238</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45159</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>44874</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>45166</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46097</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>44890</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>44672</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>44636</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41857,7 +41857,7 @@
         <v>44585</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41930,7 +41930,7 @@
         <v>44530</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42003,7 +42003,7 @@
         <v>45140</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>45080</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45070</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45645</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42295,7 +42295,7 @@
         <v>45301</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42368,7 +42368,7 @@
         <v>45043</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>45075</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45335</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45077</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45215</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42733,7 +42733,7 @@
         <v>45537</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>45166</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>45012</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42952,7 +42952,7 @@
         <v>44636</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43025,7 +43025,7 @@
         <v>45553</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43098,7 +43098,7 @@
         <v>45532</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43171,7 +43171,7 @@
         <v>45089</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43244,7 +43244,7 @@
         <v>45735</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45113</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45264</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45846</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>45846</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43619,7 +43619,7 @@
         <v>44893</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>46113</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43765,7 +43765,7 @@
         <v>46113</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>46113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46113</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43984,7 +43984,7 @@
         <v>46113</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44057,7 +44057,7 @@
         <v>44517</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>46112</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>44860</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>46113</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>45234</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>45610</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>46113</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>46113</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45538</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45538</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45351</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44543</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>44603</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>44491</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45554</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>45183</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44691</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45075</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>45783</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45517,7 +45517,7 @@
         <v>45917</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45590,7 +45590,7 @@
         <v>45579</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>45894</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>45911</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45923</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45882,7 +45882,7 @@
         <v>45002</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45955,7 +45955,7 @@
         <v>45985</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>45169</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>44741</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>46007</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>46007</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>44937</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45685</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45784</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45217</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>44580</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46685,7 +46685,7 @@
         <v>45827</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46758,7 +46758,7 @@
         <v>45968</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45784</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46904,7 +46904,7 @@
         <v>45915</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46977,7 +46977,7 @@
         <v>45884</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45980</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47123,7 +47123,7 @@
         <v>45664</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45166</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45880</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47342,7 +47342,7 @@
         <v>45035</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47415,7 +47415,7 @@
         <v>45013</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>45013</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>45225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46027</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47707,7 +47707,7 @@
         <v>44930</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47780,7 +47780,7 @@
         <v>45568</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47853,7 +47853,7 @@
         <v>45531</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47926,7 +47926,7 @@
         <v>44960</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45784</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48072,7 +48072,7 @@
         <v>45580</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45104</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>44942</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45051</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>46042</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>46042</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>46042</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>44593</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45154</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48729,7 +48729,7 @@
         <v>44875</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48802,7 +48802,7 @@
         <v>44914</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48875,7 +48875,7 @@
         <v>45106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48948,7 +48948,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>45615</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>46055</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>45537</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>44900</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49313,7 +49313,7 @@
         <v>45195</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49386,7 +49386,7 @@
         <v>45576</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49459,7 +49459,7 @@
         <v>44998</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49532,7 +49532,7 @@
         <v>45324</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>44592</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>45012</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>46051</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49829,7 +49829,7 @@
         <v>46051</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>46051</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49975,7 +49975,7 @@
         <v>46052</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50048,7 +50048,7 @@
         <v>46056</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50121,7 +50121,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50194,7 +50194,7 @@
         <v>46066</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50267,7 +50267,7 @@
         <v>46150</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50340,7 +50340,7 @@
         <v>46097</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50413,7 +50413,7 @@
         <v>46056</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50486,7 +50486,7 @@
         <v>45133</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>46077</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50632,7 +50632,7 @@
         <v>46087</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50710,7 +50710,7 @@
         <v>45832</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50783,7 +50783,7 @@
         <v>45809</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>46158</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>46058</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45809</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51075,7 +51075,7 @@
         <v>46158</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51148,7 +51148,7 @@
         <v>46158</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51221,7 +51221,7 @@
         <v>46125</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>46158</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51367,7 +51367,7 @@
         <v>46158</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51440,7 +51440,7 @@
         <v>46158</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51513,7 +51513,7 @@
         <v>45699</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>46037</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51659,7 +51659,7 @@
         <v>46162</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>46162</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51805,7 +51805,7 @@
         <v>46162</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51878,7 +51878,7 @@
         <v>44837</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>46164</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52024,7 +52024,7 @@
         <v>46164</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52097,7 +52097,7 @@
         <v>46164</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52170,7 +52170,7 @@
         <v>46169</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52243,7 +52243,7 @@
         <v>46176</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52316,7 +52316,7 @@
         <v>46177</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>46176</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>46181</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>46181</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>46183</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>46182</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>46185</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>46188</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>46188</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>46177</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>46199</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46199</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>46199</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>46206</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>46206</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>46177</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45838</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>46070</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>46265</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>46188</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>46267</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>46268</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>46268</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>46269</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>46270</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>46272</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>46274</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46230</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>45981</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46112</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>45727</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54579,7 +54579,7 @@
         <v>45495</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54652,7 +54652,7 @@
         <v>45092</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54725,7 +54725,7 @@
         <v>45887</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54798,7 +54798,7 @@
         <v>46283</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>45013</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45092</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55017,7 +55017,7 @@
         <v>46069</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55090,7 +55090,7 @@
         <v>45456</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55163,7 +55163,7 @@
         <v>45001</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55236,7 +55236,7 @@
         <v>46239</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45238</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55382,7 +55382,7 @@
         <v>45495</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55455,7 +55455,7 @@
         <v>45161</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55528,7 +55528,7 @@
         <v>45243</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55601,7 +55601,7 @@
         <v>45202</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55674,7 +55674,7 @@
         <v>45358</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>45344</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55820,7 +55820,7 @@
         <v>45162</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55893,7 +55893,7 @@
         <v>45783</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>46275</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56068,7 +56068,7 @@
         <v>45923</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56141,7 +56141,7 @@
         <v>46241</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>46283</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>45393</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56360,7 +56360,7 @@
         <v>45362</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56433,7 +56433,7 @@
         <v>45887</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>44869</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>44967</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56652,7 +56652,7 @@
         <v>45735</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56725,7 +56725,7 @@
         <v>45754</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56798,7 +56798,7 @@
         <v>44909</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45180</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45182</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57017,7 +57017,7 @@
         <v>45737</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57090,7 +57090,7 @@
         <v>46241</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>46000</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57236,7 +57236,7 @@
         <v>45971</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57309,7 +57309,7 @@
         <v>45019</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57382,7 +57382,7 @@
         <v>45069</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45093</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57528,7 +57528,7 @@
         <v>46288</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>46245</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>46287</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>46209</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57820,7 +57820,7 @@
         <v>46209</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57893,7 +57893,7 @@
         <v>46246</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57966,7 +57966,7 @@
         <v>46246</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58039,7 +58039,7 @@
         <v>46246</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58112,7 +58112,7 @@
         <v>46246</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58185,7 +58185,7 @@
         <v>46290</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58258,7 +58258,7 @@
         <v>46246</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58331,7 +58331,7 @@
         <v>45981</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58404,7 +58404,7 @@
         <v>46290</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
         <v>46290</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>46290</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>46294</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58696,7 +58696,7 @@
         <v>46294</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58842,7 +58842,7 @@
         <v>46253</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58915,7 +58915,7 @@
         <v>46182</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58988,7 +58988,7 @@
         <v>46294</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59061,7 +59061,7 @@
         <v>46253</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>46049</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>46297</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59280,7 +59280,7 @@
         <v>46254</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59353,7 +59353,7 @@
         <v>46254</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59426,7 +59426,7 @@
         <v>46302</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59499,7 +59499,7 @@
         <v>46302</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>46258</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>46258</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59718,7 +59718,7 @@
         <v>46181</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59791,7 +59791,7 @@
         <v>46304</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>46265</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>45761</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60010,7 +60010,7 @@
         <v>46111</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60083,7 +60083,7 @@
         <v>46297</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60156,7 +60156,7 @@
         <v>44831</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60234,7 +60234,7 @@
         <v>44110</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60312,7 +60312,7 @@
         <v>43938</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
         <v>44825</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45188</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>44959</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45373</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>44959</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60755,7 +60755,7 @@
         <v>45155</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60828,7 +60828,7 @@
         <v>45611</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45271</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60974,7 +60974,7 @@
         <v>45474</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>45646</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45734</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61193,7 +61193,7 @@
         <v>45702</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61266,7 +61266,7 @@
         <v>45719</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61339,7 +61339,7 @@
         <v>45734</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61412,7 +61412,7 @@
         <v>45460</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61485,7 +61485,7 @@
         <v>46064</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61558,7 +61558,7 @@
         <v>46070</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61631,7 +61631,7 @@
         <v>46097</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61704,7 +61704,7 @@
         <v>46099</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61777,7 +61777,7 @@
         <v>46099</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>46105</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61923,7 +61923,7 @@
         <v>46164</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61996,7 +61996,7 @@
         <v>46260</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62069,7 +62069,7 @@
         <v>44972</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62142,7 +62142,7 @@
         <v>44960</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62215,7 +62215,7 @@
         <v>45250</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>44981</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62361,7 +62361,7 @@
         <v>46045</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45923</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>45474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>46275</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45832</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45004</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>46142</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45961</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46158</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>45050</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>46070</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45631</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45736</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>45579</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>46280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>46069</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45337</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>46251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45625</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45561</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44959</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45474</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45611</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>46099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>46101</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45050</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44830</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44691</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44719</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>44588</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44825</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44634</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44847</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44540</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44809</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44742</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44837</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44579</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44494</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44592</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44503</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44711</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44804</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44657</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44858</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44875</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45400</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45315</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45035</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45079</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44886</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44491</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45393</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45643</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45373</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44875</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45107</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45387</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44860</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44890</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45458</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44672</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45166</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45034</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44553</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45578</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45142</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>44692</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44847</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44592</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45028</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45315</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44545</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44879</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45028</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44691</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45586</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45328</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45266</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44706</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45707</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44757</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45328</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45483</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45324</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44851</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45568</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45028</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45234</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45020</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45168</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44584</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44592</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45365</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45443</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44512</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45742</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45553</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45475</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45218</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45600</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45532</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45532</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45254</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44609</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44825</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45411</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44586</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44820</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45309</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44725</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45225</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45278</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45443</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45308</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44523</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45174</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45013</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45013</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44638</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45361</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>44619</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45685</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45576</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45784</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45880</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45923</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44636</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45968</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45342</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45707</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45917</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45095</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45749</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45526</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>44860</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45884</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45827</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45050</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45104</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45316</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45715</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45784</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45784</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45789</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45250</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>45645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45335</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45846</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45334</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45370</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45169</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45917</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45251</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45918</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45631</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45334</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45133</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45923</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45923</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45747</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45180</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45929</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45210</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45647</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>46148</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45415</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45930</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45156</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>46150</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>45937</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45012</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45945</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45945</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45945</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45350</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45035</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44742</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45343</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45106</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44628</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45089</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45148</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46097</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45832</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45954</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45133</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45957</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45958</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45958</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45958</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45958</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45958</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45106</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45961</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45809</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46125</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>46158</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45699</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45961</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45961</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45809</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45580</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45217</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45713</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45938</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46158</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46158</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46158</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45631</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46158</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45645</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46037</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45173</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45579</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45340</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44911</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45972</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45013</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46162</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45538</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45727</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45407</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44837</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45735</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45978</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45118</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45106</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45002</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44753</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46164</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45194</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44862</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45630</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46164</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45551</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46164</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45117</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45168</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45351</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45846</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45619</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45846</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46169</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45554</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45537</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45012</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44809</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>44756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45077</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45604</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45107</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44728</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45695</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46007</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>46007</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44981</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45610</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44596</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>44876</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45551</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46027</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45127</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45512</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45166</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44543</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45261</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46176</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46042</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45366</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46042</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46042</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45075</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44930</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>46055</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>46051</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>46051</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45082</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46052</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45014</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45085</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>46182</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>46056</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46183</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44614</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45007</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45007</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46066</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45551</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44691</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45085</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44799</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44641</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45077</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45537</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45538</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46188</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46185</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45166</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45251</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44631</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45463</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45463</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>46056</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44754</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45092</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>46087</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45455</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>44511</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>46097</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>44580</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45315</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45043</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45113</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44881</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44920</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46112</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>46113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>46113</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>46113</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>46113</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>46113</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>46177</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45055</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44545</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44988</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44960</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45279</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45387</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45080</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45247</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45105</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45915</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45106</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45911</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45499</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45165</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45783</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45524</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45218</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>44866</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>46206</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45264</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45188</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46206</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45093</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>45113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>44914</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45321</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>46177</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45127</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45238</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>45334</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45662</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45838</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45531</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>44991</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>44624</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>44939</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44939</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45393</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45278</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45204</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>46070</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45698</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45178</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44585</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45062</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>44893</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45394</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45344</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44820</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>46230</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45673</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45309</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46270</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46272</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45142</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44840</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45577</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45094</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45208</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45531</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45140</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45524</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45218</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>44757</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>44619</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45180</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45637</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45181</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>44825</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45309</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45747</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45090</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45324</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45170</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45042</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45406</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45162</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44893</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>46283</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46241</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45727</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45887</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45981</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>46283</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45735</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45754</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47526,7 +47526,7 @@
         <v>45887</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45393</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45456</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45495</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>46239</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>44930</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45092</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>44869</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45923</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>45202</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45019</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>44909</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45093</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45182</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45737</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45971</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45362</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45243</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45358</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45180</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45783</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45344</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>46275</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45092</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45069</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45092</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>46241</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45013</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45161</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45495</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>46069</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>46112</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46000</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>44967</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>45454</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>45169</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46246</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46246</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45573</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>46246</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>46209</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>46209</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>44517</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>46246</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45027</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45194</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>46245</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>46288</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45309</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>46246</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>44700</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45674</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45183</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44603</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51789,7 +51789,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>46290</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45393</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>44616</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45174</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45070</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45981</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46290</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46290</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45037</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>45092</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46290</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45076</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>44900</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45266</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46294</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>46182</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45571</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45565</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>44722</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46294</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>44903</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45154</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46294</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>44711</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>44693</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>44581</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45075</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46254</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45616</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45062</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>46253</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45113</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>46297</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46049</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>46294</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>46254</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45672</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45030</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45348</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>44748</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45775</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45048</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45028</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45075</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45604</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45075</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45538</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45594</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45555</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>45344</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45499</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45372</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45573</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45621</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45783</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45387</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45624</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46258</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45674</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45714</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45785</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56539,7 +56539,7 @@
         <v>44496</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>45656</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>46181</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56758,7 +56758,7 @@
         <v>45453</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45691</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>45532</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>46302</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45384</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>46258</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57196,7 +57196,7 @@
         <v>45540</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45761</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>46302</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>46304</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>46304</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>46111</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57634,7 +57634,7 @@
         <v>46297</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>46304</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>46304</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>46304</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45797</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57999,7 +57999,7 @@
         <v>45797</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>45796</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58145,7 +58145,7 @@
         <v>45693</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45581</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45770</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46304</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>46304</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45632</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45012</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45393</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58802,7 +58802,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58875,7 +58875,7 @@
         <v>46268</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58948,7 +58948,7 @@
         <v>45537</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>46267</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59094,7 +59094,7 @@
         <v>46311</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
         <v>46268</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45826</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>46269</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45812</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45839</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>45711</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59605,7 +59605,7 @@
         <v>45256</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>45812</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59751,7 +59751,7 @@
         <v>45695</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>45602</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
         <v>45602</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45789</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60043,7 +60043,7 @@
         <v>45749</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60116,7 +60116,7 @@
         <v>45873</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60189,7 +60189,7 @@
         <v>45875</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45875</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60335,7 +60335,7 @@
         <v>45883</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60408,7 +60408,7 @@
         <v>45883</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60481,7 +60481,7 @@
         <v>44825</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>43938</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60632,7 +60632,7 @@
         <v>44110</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>45188</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>44959</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45373</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61007,7 +61007,7 @@
         <v>44959</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>45155</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45611</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45271</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>45474</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61372,7 +61372,7 @@
         <v>45646</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61445,7 +61445,7 @@
         <v>45734</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>45702</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61591,7 +61591,7 @@
         <v>45719</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>45460</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>46064</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>46070</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>46097</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>46099</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>46099</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>46105</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46164</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>46260</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>44972</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62467,7 +62467,7 @@
         <v>44960</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45250</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62613,7 +62613,7 @@
         <v>44981</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>46045</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45923</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>45474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>46275</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>45358</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>45832</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>45999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44077</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>44490</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45918</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45988</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>45905</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>46111</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>46236</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>44509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>44600</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>45475</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
         <v>46064</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>46105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>45089</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>45901</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>45393</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45692</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4062,7 +4062,7 @@
         <v>44589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44980</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         <v>44742</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>44498</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44531</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>45004</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45103</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45050</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
         <v>45303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>46142</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>45961</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>46158</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45012</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45903</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>46188</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>45050</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>46112</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         <v>46070</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45917</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45631</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6614,7 +6614,7 @@
         <v>45736</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         <v>45579</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>46280</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>46069</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45085</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45110</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>45337</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>46251</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45625</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45603</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45561</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>45847</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7983,7 +7983,7 @@
         <v>44959</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45474</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8193,7 +8193,7 @@
         <v>45611</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>46064</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>46099</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>46101</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>45050</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44574</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8864,7 +8864,7 @@
         <v>44572</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44585</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>44670</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44830</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44875</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>44501</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44559</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>44526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44691</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44676</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>44502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>44719</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44503</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>44497</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>44806</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44629</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>44571</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44572</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44599</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>44491</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         <v>44588</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44516</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44719</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44825</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44634</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>44847</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>44540</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>44524</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44809</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44698</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>44621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>44859</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44742</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>44743</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44837</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44706</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44579</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44494</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12665,7 +12665,7 @@
         <v>44592</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44608</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44503</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>44711</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44804</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44614</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>44657</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>44858</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44875</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45400</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13473,7 +13473,7 @@
         <v>45315</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>45035</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45079</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44886</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>45257</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45615</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>45196</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13984,7 +13984,7 @@
         <v>44491</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14057,7 +14057,7 @@
         <v>45393</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14130,7 +14130,7 @@
         <v>44967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>45108</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>45531</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14349,7 +14349,7 @@
         <v>45643</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45373</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14495,7 +14495,7 @@
         <v>44875</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44747</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>45107</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14714,7 +14714,7 @@
         <v>45387</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>44860</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44998</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>44890</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45215</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>44937</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44741</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45458</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         <v>44946</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44939</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>44672</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>45166</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45051</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45034</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>44553</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         <v>45159</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>44986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45578</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45142</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>44692</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>45198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>44847</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>45002</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>44592</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45028</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45315</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>44545</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44879</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45028</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44691</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45586</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>45328</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45075</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>45266</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>44706</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45335</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45707</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>44757</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>45328</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>45107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>45483</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45324</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44851</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>44593</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45541</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45568</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45028</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45234</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44636</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>45020</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45168</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44988</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44584</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44592</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45365</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>45443</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>44512</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44587</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45610</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>45742</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45553</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45475</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45218</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>44974</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45600</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19829,7 +19829,7 @@
         <v>45532</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45532</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19975,7 +19975,7 @@
         <v>45245</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45204</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45218</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45532</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45254</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45048</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45537</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>44609</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44609</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>44825</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45085</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45085</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45411</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45697</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44586</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>44820</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21153,7 +21153,7 @@
         <v>45309</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21226,7 +21226,7 @@
         <v>44725</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44516</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45225</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45278</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45443</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45308</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44523</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45174</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45013</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45013</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44638</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45512</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45361</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>44619</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45685</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45576</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>45784</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45894</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45162</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45880</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45923</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44636</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45968</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45342</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45707</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45917</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45095</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45664</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45749</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23343,7 +23343,7 @@
         <v>45526</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>44860</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45884</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>45980</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23635,7 +23635,7 @@
         <v>45827</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45050</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23781,7 +23781,7 @@
         <v>45104</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>45251</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45316</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>45715</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>45784</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45784</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24219,7 +24219,7 @@
         <v>45789</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24292,7 +24292,7 @@
         <v>45250</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>45084</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24438,7 +24438,7 @@
         <v>45645</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45335</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45846</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         <v>45334</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45908</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>44747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>45370</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>45169</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>45917</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45251</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>44551</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>45918</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25314,7 +25314,7 @@
         <v>45631</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45334</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>45133</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45917</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>44874</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45923</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45923</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45747</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45180</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45166</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45929</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26263,7 +26263,7 @@
         <v>45210</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26409,7 +26409,7 @@
         <v>45647</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26482,7 +26482,7 @@
         <v>46148</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>45415</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45930</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>45091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45156</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>46150</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>45937</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45012</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45159</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45728</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45945</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27285,7 +27285,7 @@
         <v>45945</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45945</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45350</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27577,7 +27577,7 @@
         <v>45035</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27650,7 +27650,7 @@
         <v>44742</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45343</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27796,7 +27796,7 @@
         <v>45106</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>44628</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27942,7 +27942,7 @@
         <v>45089</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>44636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>45148</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>46097</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45832</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45954</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45133</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46077</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>45957</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45958</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>45958</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28745,7 +28745,7 @@
         <v>45958</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28818,7 +28818,7 @@
         <v>45958</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28891,7 +28891,7 @@
         <v>45958</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>45958</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45106</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45961</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45809</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>46125</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>46158</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45699</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45961</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29548,7 +29548,7 @@
         <v>45645</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29621,7 +29621,7 @@
         <v>45961</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45809</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29767,7 +29767,7 @@
         <v>45580</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>45217</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29913,7 +29913,7 @@
         <v>45713</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45938</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45212</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30132,7 +30132,7 @@
         <v>46158</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>46158</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>46158</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45631</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46158</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45645</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>46037</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45173</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>46058</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>45579</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45340</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44911</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>45972</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45013</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46162</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>45538</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>45727</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45407</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44837</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45735</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31592,7 +31592,7 @@
         <v>45978</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46162</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>45118</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45106</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31957,7 +31957,7 @@
         <v>45002</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32030,7 +32030,7 @@
         <v>44936</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32103,7 +32103,7 @@
         <v>44753</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32176,7 +32176,7 @@
         <v>46164</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45194</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44862</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45106</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45630</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>46164</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45551</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>46164</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45117</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45168</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45351</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45846</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45619</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45846</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>45154</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44530</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>46169</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>45554</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33500,7 +33500,7 @@
         <v>45537</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33573,7 +33573,7 @@
         <v>45012</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33646,7 +33646,7 @@
         <v>44809</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>44756</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45077</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>45604</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34011,7 +34011,7 @@
         <v>45107</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44728</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34157,7 +34157,7 @@
         <v>45695</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46007</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34303,7 +34303,7 @@
         <v>45469</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34376,7 +34376,7 @@
         <v>46007</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>44981</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34522,7 +34522,7 @@
         <v>45610</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44596</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45610</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>44876</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34819,7 +34819,7 @@
         <v>45551</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>46027</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
         <v>45127</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45512</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45166</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>44543</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45261</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>46176</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>46176</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>46177</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>46042</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45366</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>46042</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>46042</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45075</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>44930</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>46055</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>46051</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>46051</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45082</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>46051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46052</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45014</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36571,7 +36571,7 @@
         <v>45085</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36717,7 +36717,7 @@
         <v>46182</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36790,7 +36790,7 @@
         <v>46181</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>46056</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>46183</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45107</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44614</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>45007</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
         <v>45007</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37301,7 +37301,7 @@
         <v>45215</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37374,7 +37374,7 @@
         <v>46066</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37447,7 +37447,7 @@
         <v>45551</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37520,7 +37520,7 @@
         <v>44691</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37593,7 +37593,7 @@
         <v>45085</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44799</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37739,7 +37739,7 @@
         <v>44641</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37812,7 +37812,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45077</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37958,7 +37958,7 @@
         <v>45537</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         <v>45538</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38104,7 +38104,7 @@
         <v>46188</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38177,7 +38177,7 @@
         <v>45170</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>46185</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45166</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>45251</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44631</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38542,7 +38542,7 @@
         <v>45463</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>45463</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>46056</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>44754</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45092</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38980,7 +38980,7 @@
         <v>46087</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45455</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39204,7 +39204,7 @@
         <v>45238</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39277,7 +39277,7 @@
         <v>44511</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>46097</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39423,7 +39423,7 @@
         <v>44580</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>45315</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45043</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>45113</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>44881</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44920</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>46112</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>46113</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>46113</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>46113</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>46113</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>46113</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>46113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>46113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>46177</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45055</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>46199</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>44545</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>46199</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40883,7 +40883,7 @@
         <v>44988</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44960</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45279</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41102,7 +41102,7 @@
         <v>46199</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41175,7 +41175,7 @@
         <v>45387</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>45080</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>45247</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45105</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45915</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>45106</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45911</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>45499</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>45165</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>45783</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45524</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45985</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45218</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>44866</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>46206</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45264</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45188</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>46206</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45093</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42562,7 +42562,7 @@
         <v>45113</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42635,7 +42635,7 @@
         <v>44914</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45321</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>46177</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>45127</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>45238</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43000,7 +43000,7 @@
         <v>45334</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>45662</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45838</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43219,7 +43219,7 @@
         <v>45531</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>44991</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>44624</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
         <v>44939</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44939</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43584,7 +43584,7 @@
         <v>45393</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43657,7 +43657,7 @@
         <v>45278</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43730,7 +43730,7 @@
         <v>45204</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>46070</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43876,7 +43876,7 @@
         <v>45698</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45178</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44585</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44095,7 +44095,7 @@
         <v>45062</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44168,7 +44168,7 @@
         <v>44893</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46188</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>45394</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45344</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>44820</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44533,7 +44533,7 @@
         <v>46230</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45673</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44679,7 +44679,7 @@
         <v>45309</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44752,7 +44752,7 @@
         <v>46270</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44825,7 +44825,7 @@
         <v>46272</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44898,7 +44898,7 @@
         <v>45142</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44840</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45044,7 +45044,7 @@
         <v>45577</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45117,7 +45117,7 @@
         <v>45094</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45190,7 +45190,7 @@
         <v>45208</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46274</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>45531</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>45140</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45482,7 +45482,7 @@
         <v>45524</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45218</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>44757</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45701,7 +45701,7 @@
         <v>44619</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45180</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>45637</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45181</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>44825</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>45309</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>45747</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45090</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>45324</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45223</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45170</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45042</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45406</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>45162</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>44893</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45092</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46942,7 +46942,7 @@
         <v>46283</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>46241</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
         <v>45727</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>45887</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45981</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>46283</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45735</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47453,7 +47453,7 @@
         <v>45754</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47526,7 +47526,7 @@
         <v>45887</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47599,7 +47599,7 @@
         <v>45393</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45456</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45495</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>46239</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>44930</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45092</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>44869</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>45923</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48183,7 +48183,7 @@
         <v>45202</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48256,7 +48256,7 @@
         <v>45019</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48329,7 +48329,7 @@
         <v>44909</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48402,7 +48402,7 @@
         <v>45093</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>45182</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>45737</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45971</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45362</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48767,7 +48767,7 @@
         <v>45243</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45358</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48913,7 +48913,7 @@
         <v>45001</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>46287</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45238</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45180</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45783</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45344</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>46275</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49453,7 +49453,7 @@
         <v>45092</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45069</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49599,7 +49599,7 @@
         <v>45092</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>46241</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>45013</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49818,7 +49818,7 @@
         <v>45162</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45161</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45495</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -50037,7 +50037,7 @@
         <v>46069</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50110,7 +50110,7 @@
         <v>46112</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>46000</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50256,7 +50256,7 @@
         <v>44967</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50329,7 +50329,7 @@
         <v>45454</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>45169</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46246</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>46246</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45573</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50694,7 +50694,7 @@
         <v>46246</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50767,7 +50767,7 @@
         <v>46209</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50840,7 +50840,7 @@
         <v>46209</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50913,7 +50913,7 @@
         <v>44517</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>46246</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45027</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45194</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51205,7 +51205,7 @@
         <v>46245</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51278,7 +51278,7 @@
         <v>46288</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45309</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51424,7 +51424,7 @@
         <v>46246</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51497,7 +51497,7 @@
         <v>44700</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>45674</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45183</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44603</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51789,7 +51789,7 @@
         <v>45225</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>46290</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>45393</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -52008,7 +52008,7 @@
         <v>44616</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52081,7 +52081,7 @@
         <v>45174</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52154,7 +52154,7 @@
         <v>45070</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52227,7 +52227,7 @@
         <v>45981</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>46290</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52373,7 +52373,7 @@
         <v>46290</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>45037</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52519,7 +52519,7 @@
         <v>45092</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>46290</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52665,7 +52665,7 @@
         <v>45076</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52738,7 +52738,7 @@
         <v>44900</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52811,7 +52811,7 @@
         <v>45266</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46294</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>46182</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -53030,7 +53030,7 @@
         <v>45571</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>45565</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53176,7 +53176,7 @@
         <v>44722</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53249,7 +53249,7 @@
         <v>46294</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53322,7 +53322,7 @@
         <v>44903</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>45154</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53468,7 +53468,7 @@
         <v>46294</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53541,7 +53541,7 @@
         <v>44711</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>44693</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53687,7 +53687,7 @@
         <v>44581</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45075</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53833,7 +53833,7 @@
         <v>46254</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53906,7 +53906,7 @@
         <v>45616</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53979,7 +53979,7 @@
         <v>45062</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54052,7 +54052,7 @@
         <v>46253</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>45113</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>46297</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46049</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>46294</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>46254</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45672</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>45301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45030</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45348</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>44748</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45775</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45048</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45028</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45075</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45604</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45075</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45538</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55439,7 +55439,7 @@
         <v>45594</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55512,7 +55512,7 @@
         <v>45555</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55585,7 +55585,7 @@
         <v>45344</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45499</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45372</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55809,7 +55809,7 @@
         <v>45573</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55882,7 +55882,7 @@
         <v>45621</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55955,7 +55955,7 @@
         <v>45783</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -56028,7 +56028,7 @@
         <v>45387</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45624</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>46258</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56247,7 +56247,7 @@
         <v>45674</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56320,7 +56320,7 @@
         <v>45714</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45631</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>45785</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56539,7 +56539,7 @@
         <v>44496</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56612,7 +56612,7 @@
         <v>45656</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56685,7 +56685,7 @@
         <v>46181</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56758,7 +56758,7 @@
         <v>45453</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>45691</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56904,7 +56904,7 @@
         <v>45532</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>46302</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57050,7 +57050,7 @@
         <v>45384</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57123,7 +57123,7 @@
         <v>46258</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57196,7 +57196,7 @@
         <v>45540</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57269,7 +57269,7 @@
         <v>45761</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57342,7 +57342,7 @@
         <v>46302</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>46304</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>46304</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>46111</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57634,7 +57634,7 @@
         <v>46297</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57707,7 +57707,7 @@
         <v>46304</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>46304</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57853,7 +57853,7 @@
         <v>46304</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57926,7 +57926,7 @@
         <v>45797</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57999,7 +57999,7 @@
         <v>45797</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58072,7 +58072,7 @@
         <v>45796</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58145,7 +58145,7 @@
         <v>45693</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>45581</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58291,7 +58291,7 @@
         <v>45770</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58364,7 +58364,7 @@
         <v>46304</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>46304</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58510,7 +58510,7 @@
         <v>45632</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45012</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45393</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58729,7 +58729,7 @@
         <v>46265</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58802,7 +58802,7 @@
         <v>46265</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58875,7 +58875,7 @@
         <v>46268</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58948,7 +58948,7 @@
         <v>45537</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>46267</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59094,7 +59094,7 @@
         <v>46311</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59167,7 +59167,7 @@
         <v>46268</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45826</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>46269</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45812</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45839</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59532,7 +59532,7 @@
         <v>45711</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59605,7 +59605,7 @@
         <v>45256</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59678,7 +59678,7 @@
         <v>45812</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59751,7 +59751,7 @@
         <v>45695</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>45602</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59897,7 +59897,7 @@
         <v>45602</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59970,7 +59970,7 @@
         <v>45789</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -60043,7 +60043,7 @@
         <v>45749</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60116,7 +60116,7 @@
         <v>45873</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60189,7 +60189,7 @@
         <v>45875</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60262,7 +60262,7 @@
         <v>45875</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60335,7 +60335,7 @@
         <v>45883</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60408,7 +60408,7 @@
         <v>45883</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60481,7 +60481,7 @@
         <v>44825</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60559,7 +60559,7 @@
         <v>43938</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60632,7 +60632,7 @@
         <v>44110</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60710,7 +60710,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>45188</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>44959</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45373</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -61007,7 +61007,7 @@
         <v>44959</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>45155</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45611</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45271</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61299,7 +61299,7 @@
         <v>45474</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61372,7 +61372,7 @@
         <v>45646</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61445,7 +61445,7 @@
         <v>45734</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61518,7 +61518,7 @@
         <v>45702</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61591,7 +61591,7 @@
         <v>45719</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61664,7 +61664,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61737,7 +61737,7 @@
         <v>45460</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61810,7 +61810,7 @@
         <v>46064</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61883,7 +61883,7 @@
         <v>46070</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>46097</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>46099</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>46099</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>46105</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46164</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>46260</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>44972</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62467,7 +62467,7 @@
         <v>44960</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45250</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62613,7 +62613,7 @@
         <v>44981</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62686,7 +62686,7 @@
         <v>46045</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45923</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>45474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>44077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45832</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46111</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46236</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44509</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>44600</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45475</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>46064</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>46105</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45393</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45692</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>44980</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>44742</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44498</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44531</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46158</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45085</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45961</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45387</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45625</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45603</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46069</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45337</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45561</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>46112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>46125</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45905</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>46142</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45012</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45004</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45103</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45050</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45736</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44830</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44676</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44502</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44599</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44588</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44634</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44847</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>44540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44524</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44621</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44837</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44706</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44579</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44494</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44592</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44804</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45075</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44657</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44858</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>44875</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45180</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45579</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45713</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45247</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45715</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45512</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45002</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45334</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>44741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45217</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44825</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45208</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45166</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45035</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44881</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45407</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45013</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45225</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45204</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45908</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>46158</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46158</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46037</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>44837</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>46164</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46164</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46164</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45918</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45580</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44942</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45051</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45923</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45321</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45154</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44875</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44914</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45106</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>46169</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45092</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45615</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45195</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45324</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44592</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45012</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45166</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>44860</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46176</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44847</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45393</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45945</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45340</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45411</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45387</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44876</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45455</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45945</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45159</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45048</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45257</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45526</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>44903</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45370</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46181</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45674</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45454</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>46183</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45958</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45958</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45957</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45958</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45958</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45458</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45028</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45961</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45961</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46188</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45961</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45551</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46188</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45168</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45672</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45537</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45254</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45662</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45251</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45972</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45223</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45619</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46199</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45707</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45443</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46199</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45328</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45393</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45106</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45085</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45082</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45118</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45571</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45007</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46206</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45727</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45250</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45846</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45698</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45194</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45127</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45443</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45695</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>46177</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45838</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45342</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45165</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46070</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45075</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45538</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45604</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45621</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45555</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45075</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45344</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45372</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45499</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45594</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45573</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45387</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46230</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46007</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46007</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45540</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45384</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45624</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45631</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45691</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45532</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45453</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45785</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45656</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>46027</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45674</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44496</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45981</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>46112</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45727</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45495</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45092</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>46283</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45013</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45092</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>46069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45456</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46239</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45238</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45495</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45161</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45243</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45202</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45358</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45344</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45162</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45783</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45923</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46241</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46283</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45393</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45362</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45887</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44869</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45735</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45754</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>44909</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45180</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45182</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45737</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>46241</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46042</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46042</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45019</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45069</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46288</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46245</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>46055</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45797</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45797</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45581</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45770</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45693</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45632</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46246</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46246</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46051</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45393</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45309</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>46290</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>46052</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46246</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45981</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46290</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>46056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46294</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>46294</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>46066</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45537</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46294</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>46253</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45826</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46056</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46253</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45812</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46049</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>46087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>46297</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45256</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>45113</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>46254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45839</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>46097</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45711</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45695</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45812</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46302</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46302</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46113</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46113</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46113</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46258</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46113</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46113</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45475</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46112</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46113</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46113</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46113</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45512</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45602</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45602</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45789</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45030</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>46181</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45749</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45873</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45761</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45875</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45875</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>46265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>46265</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45499</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>44893</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45373</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45524</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44592</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44619</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45647</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>45551</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46304</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45783</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44584</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45674</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>46304</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46304</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45917</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46304</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46304</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45077</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>44614</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46304</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>46304</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45894</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45911</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45645</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45645</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45923</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45985</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45685</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45784</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45827</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45968</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45784</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45915</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>45884</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>46268</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45980</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45664</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44691</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>44587</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45007</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45880</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45742</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46267</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>46313</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44939</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45028</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>45028</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>46311</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>46269</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45784</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44692</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46268</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>46270</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45565</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44911</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45261</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46275</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45637</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45789</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46315</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>46297</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>46315</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46294</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>44974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44693</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>46318</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45576</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45169</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46315</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44920</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45324</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46274</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45251</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46318</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>44986</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46148</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45057</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45142</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45218</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>46150</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44756</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46097</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>44638</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45251</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45586</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>44619</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45009</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45133</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>46077</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>44967</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45350</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45309</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45316</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44700</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45832</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45809</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>46158</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>46058</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45809</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45092</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46158</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>46158</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45308</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45107</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45079</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45604</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>44757</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45117</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44936</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45055</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45062</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45178</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45728</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>44747</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>44820</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45028</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44988</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>44840</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44516</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45188</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45027</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45113</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45204</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>44930</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44748</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45215</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45238</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>44890</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>44530</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45080</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45075</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45077</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45537</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45166</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45012</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>44636</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>45553</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45532</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45735</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>45113</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45264</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>44860</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45234</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45085</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45538</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45538</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45541</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45400</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45406</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45013</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44609</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45092</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>44847</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45105</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>45106</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>45093</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45108</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45013</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45050</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45245</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>44545</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45344</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>44551</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45106</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45393</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45387</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45551</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45107</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45107</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>45469</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44628</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45107</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45002</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45133</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45577</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44879</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45020</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45537</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45156</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45394</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45531</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45035</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45035</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>44981</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>45014</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45524</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45084</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45106</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45573</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45127</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45415</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>44512</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45048</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45076</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45174</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45170</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45278</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45181</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44581</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45335</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45334</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44511</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45610</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45028</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44596</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45218</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45673</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45218</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44553</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45075</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>44641</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44523</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45328</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>44624</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45747</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45162</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45315</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>44799</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45610</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44636</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45366</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45092</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>44586</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45168</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45170</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45194</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>44754</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45062</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>45196</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45090</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56422,7 +56422,7 @@
         <v>45198</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>44725</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>44706</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45707</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45210</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56787,7 +56787,7 @@
         <v>45775</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>45531</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>45578</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57006,7 +57006,7 @@
         <v>45166</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57079,7 +57079,7 @@
         <v>45173</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>44616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>44728</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>45697</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44742</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>44809</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>44757</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>44631</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45463</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45463</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>45238</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45180</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>44820</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>44722</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45309</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>44930</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45365</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45630</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45361</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>44862</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>44886</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>44946</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>45348</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>44851</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>44753</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45309</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59050,7 +59050,7 @@
         <v>45278</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>45159</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>44874</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45166</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>44672</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>44636</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>44585</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>45140</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45070</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59707,7 +59707,7 @@
         <v>45645</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45301</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45335</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>45215</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>45089</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>44893</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>44517</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45610</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45351</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60364,7 +60364,7 @@
         <v>44543</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>44603</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45183</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>44691</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>44110</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>43938</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>44825</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45188</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>45373</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>45155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>45611</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45271</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>45474</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61547,7 +61547,7 @@
         <v>45646</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45702</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61766,7 +61766,7 @@
         <v>45719</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45734</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>45460</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>46064</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62058,7 +62058,7 @@
         <v>46070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62131,7 +62131,7 @@
         <v>46097</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         <v>46099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62277,7 +62277,7 @@
         <v>46099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>46105</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>46164</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62496,7 +62496,7 @@
         <v>44972</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>44960</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62642,7 +62642,7 @@
         <v>45250</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>44981</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62788,7 +62788,7 @@
         <v>46045</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62861,7 +62861,7 @@
         <v>46260</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>

--- a/Översikt KARLSKRONA.xlsx
+++ b/Översikt KARLSKRONA.xlsx
@@ -601,7 +601,7 @@
         <v>46196</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>46119</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v>46282</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
         <v>45923</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>45474</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45358</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>46275</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>44077</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>45999</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>45832</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>45996</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>45918</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45988</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>45905</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>46111</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>46236</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>44509</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>44600</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>45475</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>46182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>44960</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>46064</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>46105</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>45901</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45393</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>45037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>44930</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>45089</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>45692</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44589</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>44980</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         <v>44742</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         <v>44498</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>44531</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46158</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45085</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45961</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
         <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45387</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45903</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45625</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45603</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>46280</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>46069</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45337</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>46251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45561</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>46112</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>46125</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>46070</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>45050</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45917</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>45905</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>46142</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>45579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45012</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>45004</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>45103</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>45631</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>45050</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45303</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45736</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>45002</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44959</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>45474</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>45611</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>46064</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8286,7 +8286,7 @@
         <v>46099</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>46101</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45050</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44574</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44572</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         <v>44551</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>44585</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44585</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8966,7 +8966,7 @@
         <v>44670</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         <v>44687</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44830</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44875</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44875</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44501</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44526</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44691</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44659</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44676</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44629</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44502</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44719</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44503</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44497</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44806</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44874</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44742</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44629</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44501</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44599</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44588</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44516</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44623</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44719</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44825</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44634</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>44847</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11375,7 +11375,7 @@
         <v>44540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>44524</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44621</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44859</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44743</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44837</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12037,7 +12037,7 @@
         <v>44706</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
         <v>44579</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44608</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44494</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>44687</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>44596</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44592</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44608</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>44711</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44804</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>44614</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45075</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44657</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>44858</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>44875</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45883</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45883</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45749</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45180</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>45579</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45334</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45713</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45247</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45715</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>45512</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13940,7 +13940,7 @@
         <v>45002</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44825</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>45169</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>45334</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>44741</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>44937</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45042</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45217</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
         <v>45532</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>45532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44580</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>44825</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45208</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45166</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45035</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44881</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45407</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45013</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>45225</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45846</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45204</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45908</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44747</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>46158</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46158</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45699</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>46037</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16057,7 +16057,7 @@
         <v>44930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>46162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>46162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45568</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>46162</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16422,7 +16422,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16495,7 +16495,7 @@
         <v>44960</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         <v>44837</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16641,7 +16641,7 @@
         <v>46164</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>45917</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46164</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>46164</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>45918</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>45580</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45104</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44942</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17225,7 +17225,7 @@
         <v>45051</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>45917</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45923</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44593</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45923</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>45321</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45154</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44875</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17809,7 +17809,7 @@
         <v>45747</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>44914</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45106</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45925</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>45930</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>46169</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>45929</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>45092</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
         <v>45929</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18466,7 +18466,7 @@
         <v>45615</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>45537</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45195</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18758,7 +18758,7 @@
         <v>44998</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45324</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18904,7 +18904,7 @@
         <v>44592</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18982,7 +18982,7 @@
         <v>45937</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19055,7 +19055,7 @@
         <v>45012</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19128,7 +19128,7 @@
         <v>45166</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19201,7 +19201,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46176</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19347,7 +19347,7 @@
         <v>44860</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>46177</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>46176</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44847</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45393</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>45945</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19785,7 +19785,7 @@
         <v>45340</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>45411</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45387</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20004,7 +20004,7 @@
         <v>44876</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20077,7 +20077,7 @@
         <v>45455</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20150,7 +20150,7 @@
         <v>45945</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45945</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45159</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>45048</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45257</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>44866</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45526</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
         <v>44903</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
         <v>45370</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20880,7 +20880,7 @@
         <v>46181</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20953,7 +20953,7 @@
         <v>45674</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45454</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>44991</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45954</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>46183</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>46182</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45958</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45958</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45958</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45957</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45266</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45958</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45958</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45458</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45028</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45961</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45961</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>46188</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>45961</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45551</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46188</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>45938</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45168</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45672</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45537</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45254</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45174</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45662</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45251</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45972</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45223</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45094</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45212</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45978</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45619</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>46199</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45707</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45443</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46199</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45328</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>45034</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45393</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45154</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44545</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24530,7 +24530,7 @@
         <v>45106</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45085</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45085</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>45082</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24822,7 +24822,7 @@
         <v>45483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24895,7 +24895,7 @@
         <v>45118</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45571</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45007</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>46206</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45727</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45250</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45846</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45846</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45698</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25781,7 +25781,7 @@
         <v>45194</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45315</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45127</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45443</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>45695</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>46177</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45838</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45342</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45165</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46070</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45075</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45538</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45604</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>45621</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45555</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45075</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45344</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45372</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45499</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45594</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45573</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>46188</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45387</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46230</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45783</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>46007</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46007</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45540</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45384</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45624</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>45714</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45631</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>45691</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45532</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28487,7 +28487,7 @@
         <v>45453</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         <v>45785</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45656</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28706,7 +28706,7 @@
         <v>46027</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28779,7 +28779,7 @@
         <v>45674</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>44496</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>45981</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         <v>46112</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29071,7 +29071,7 @@
         <v>45727</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29144,7 +29144,7 @@
         <v>45495</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29217,7 +29217,7 @@
         <v>45092</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29290,7 +29290,7 @@
         <v>45887</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29363,7 +29363,7 @@
         <v>46283</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29436,7 +29436,7 @@
         <v>45013</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45092</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>46069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45456</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>45001</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>46239</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45238</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45796</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30020,7 +30020,7 @@
         <v>45495</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30093,7 +30093,7 @@
         <v>45161</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30166,7 +30166,7 @@
         <v>45243</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         <v>45202</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45358</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45344</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -30458,7 +30458,7 @@
         <v>45162</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -30531,7 +30531,7 @@
         <v>45783</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45923</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46241</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46283</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30823,7 +30823,7 @@
         <v>45393</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45362</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>45887</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44869</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45735</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45754</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31334,7 +31334,7 @@
         <v>44909</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -31407,7 +31407,7 @@
         <v>45180</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -31480,7 +31480,7 @@
         <v>45182</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -31553,7 +31553,7 @@
         <v>45737</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>46241</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>46042</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>46042</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>46042</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31918,7 +31918,7 @@
         <v>46000</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31991,7 +31991,7 @@
         <v>45971</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45019</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45069</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32210,7 +32210,7 @@
         <v>45093</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32283,7 +32283,7 @@
         <v>46288</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -32356,7 +32356,7 @@
         <v>46245</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -32502,7 +32502,7 @@
         <v>46055</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45797</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45797</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45581</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>46209</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46209</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45770</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>46246</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45693</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45632</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45012</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>46246</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -33451,7 +33451,7 @@
         <v>46246</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>46246</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46051</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45393</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45309</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>46051</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>46290</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>46052</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>46246</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45981</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>46290</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34254,7 +34254,7 @@
         <v>46290</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>46056</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>46290</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>46294</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>46294</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>46066</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45537</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46294</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>46253</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45826</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46056</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>46253</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45812</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>46049</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>46087</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>46297</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -35427,7 +35427,7 @@
         <v>45256</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>45113</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -35573,7 +35573,7 @@
         <v>46254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45839</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35719,7 +35719,7 @@
         <v>46097</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45711</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>46254</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>45695</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45812</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>46302</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46302</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>46258</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46113</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>46113</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46113</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>46258</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46113</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>46113</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>44939</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44939</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45475</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36960,7 +36960,7 @@
         <v>46112</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>46113</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>46113</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46113</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45512</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>45602</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -37398,7 +37398,7 @@
         <v>45602</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45789</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45030</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>46181</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37690,7 +37690,7 @@
         <v>45749</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>45873</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45761</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45875</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37982,7 +37982,7 @@
         <v>45875</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>44609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>46265</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -38206,7 +38206,7 @@
         <v>46265</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -38279,7 +38279,7 @@
         <v>45499</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>44893</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45373</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45524</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>44592</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>44619</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45647</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45162</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>45551</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46304</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45783</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44584</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45674</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>46304</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -39301,7 +39301,7 @@
         <v>46304</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -39374,7 +39374,7 @@
         <v>44988</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -39447,7 +39447,7 @@
         <v>45917</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>46304</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>46304</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39666,7 +39666,7 @@
         <v>45077</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>44614</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46304</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>46304</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>45894</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45911</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45645</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45645</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -40250,7 +40250,7 @@
         <v>45923</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45985</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45685</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -40469,7 +40469,7 @@
         <v>45784</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45827</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -40615,7 +40615,7 @@
         <v>45968</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40688,7 +40688,7 @@
         <v>45784</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40761,7 +40761,7 @@
         <v>45915</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>45884</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40907,7 +40907,7 @@
         <v>46268</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45980</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45664</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44691</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>44587</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -41272,7 +41272,7 @@
         <v>45007</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -41345,7 +41345,7 @@
         <v>45880</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -41418,7 +41418,7 @@
         <v>45616</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45742</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>46267</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41637,7 +41637,7 @@
         <v>46313</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41710,7 +41710,7 @@
         <v>44939</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41783,7 +41783,7 @@
         <v>45028</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>45028</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>46311</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>46269</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45784</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>44692</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>46268</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>46270</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>45565</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>44911</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45261</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>46272</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>46275</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42761,7 +42761,7 @@
         <v>45637</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45789</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>46315</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>46297</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>46315</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -43126,7 +43126,7 @@
         <v>46294</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>44974</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -43272,7 +43272,7 @@
         <v>44693</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -43345,7 +43345,7 @@
         <v>46318</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45576</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -43491,7 +43491,7 @@
         <v>45169</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -43564,7 +43564,7 @@
         <v>46315</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>44920</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>46182</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43783,7 +43783,7 @@
         <v>45324</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46111</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>46274</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44002,7 +44002,7 @@
         <v>45037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -44075,7 +44075,7 @@
         <v>45251</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>46318</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>44986</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -44294,7 +44294,7 @@
         <v>46148</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -44367,7 +44367,7 @@
         <v>45057</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -44440,7 +44440,7 @@
         <v>45142</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>45218</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>46150</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>45085</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44732,7 +44732,7 @@
         <v>44756</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46097</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44878,7 +44878,7 @@
         <v>44638</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45251</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45586</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>44619</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>45009</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45133</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -45316,7 +45316,7 @@
         <v>45279</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>46077</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>44967</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45350</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -45608,7 +45608,7 @@
         <v>45309</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>45316</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45754,7 +45754,7 @@
         <v>44700</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45827,7 +45827,7 @@
         <v>45832</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45809</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45973,7 +45973,7 @@
         <v>46158</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>46058</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45809</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45092</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46158</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -46338,7 +46338,7 @@
         <v>46158</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -46411,7 +46411,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45308</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45107</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -46630,7 +46630,7 @@
         <v>45079</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45604</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45266</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>44757</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>45117</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44936</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45055</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -47141,7 +47141,7 @@
         <v>45062</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -47214,7 +47214,7 @@
         <v>45142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -47287,7 +47287,7 @@
         <v>45631</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45178</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45728</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>44747</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -47579,7 +47579,7 @@
         <v>44820</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45028</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>44988</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>44840</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>44516</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>45188</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45027</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45113</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45204</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>44930</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -48382,7 +48382,7 @@
         <v>44748</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>45215</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45238</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -48601,7 +48601,7 @@
         <v>44890</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -48674,7 +48674,7 @@
         <v>44530</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45080</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48820,7 +48820,7 @@
         <v>45043</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48893,7 +48893,7 @@
         <v>45075</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48966,7 +48966,7 @@
         <v>45077</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -49039,7 +49039,7 @@
         <v>45537</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -49112,7 +49112,7 @@
         <v>45166</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -49185,7 +49185,7 @@
         <v>45012</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -49258,7 +49258,7 @@
         <v>44636</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -49331,7 +49331,7 @@
         <v>45553</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -49404,7 +49404,7 @@
         <v>45532</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45735</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -49550,7 +49550,7 @@
         <v>45113</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45264</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49696,7 +49696,7 @@
         <v>44860</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>45234</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>45085</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45538</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>45538</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -50061,7 +50061,7 @@
         <v>45091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -50134,7 +50134,7 @@
         <v>45541</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45400</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45406</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -50353,7 +50353,7 @@
         <v>45013</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44609</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -50504,7 +50504,7 @@
         <v>45092</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>44847</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>45105</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>45106</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>45093</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>45108</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>45013</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>45050</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45245</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -51161,7 +51161,7 @@
         <v>44545</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -51234,7 +51234,7 @@
         <v>45344</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -51307,7 +51307,7 @@
         <v>44551</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45106</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>45393</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45387</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45551</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45107</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45107</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>45469</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44628</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45107</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45002</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>45133</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45577</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44879</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45020</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45537</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45156</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45394</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45531</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>45035</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45035</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>44981</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>45014</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45524</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45084</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45106</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45573</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45127</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45415</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>44512</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>45048</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45076</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>45174</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45170</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>45278</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45181</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44581</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45335</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45334</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>44511</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45610</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45028</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44596</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45218</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>45673</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45218</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>44553</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45075</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>44641</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44523</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45328</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>44624</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45747</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45162</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45315</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>44799</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45610</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>44636</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>45366</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45092</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>44586</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45168</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>45170</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>45194</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55984,7 +55984,7 @@
         <v>45095</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -56057,7 +56057,7 @@
         <v>45643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -56130,7 +56130,7 @@
         <v>44754</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -56203,7 +56203,7 @@
         <v>45062</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -56276,7 +56276,7 @@
         <v>45196</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -56349,7 +56349,7 @@
         <v>45090</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -56422,7 +56422,7 @@
         <v>45198</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -56495,7 +56495,7 @@
         <v>44725</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -56568,7 +56568,7 @@
         <v>44706</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45707</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56714,7 +56714,7 @@
         <v>45210</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56787,7 +56787,7 @@
         <v>45775</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56860,7 +56860,7 @@
         <v>45531</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56933,7 +56933,7 @@
         <v>45578</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -57006,7 +57006,7 @@
         <v>45166</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -57079,7 +57079,7 @@
         <v>45173</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>44616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>44728</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -57298,7 +57298,7 @@
         <v>45697</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -57371,7 +57371,7 @@
         <v>44742</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -57444,7 +57444,7 @@
         <v>44809</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>44711</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -57590,7 +57590,7 @@
         <v>44757</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>44631</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57736,7 +57736,7 @@
         <v>45463</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57809,7 +57809,7 @@
         <v>45463</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57882,7 +57882,7 @@
         <v>45238</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57955,7 +57955,7 @@
         <v>45180</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -58028,7 +58028,7 @@
         <v>44820</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>44722</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>45309</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>44930</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -58320,7 +58320,7 @@
         <v>45365</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -58393,7 +58393,7 @@
         <v>45630</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45361</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -58539,7 +58539,7 @@
         <v>44862</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>44886</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58685,7 +58685,7 @@
         <v>44946</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58758,7 +58758,7 @@
         <v>45348</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58831,7 +58831,7 @@
         <v>44851</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58904,7 +58904,7 @@
         <v>44753</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45309</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -59050,7 +59050,7 @@
         <v>45278</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -59123,7 +59123,7 @@
         <v>45159</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -59196,7 +59196,7 @@
         <v>44874</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -59269,7 +59269,7 @@
         <v>45166</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -59342,7 +59342,7 @@
         <v>44672</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -59415,7 +59415,7 @@
         <v>44636</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>44585</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>45140</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59634,7 +59634,7 @@
         <v>45070</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59707,7 +59707,7 @@
         <v>45645</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59780,7 +59780,7 @@
         <v>45301</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59853,7 +59853,7 @@
         <v>45335</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59926,7 +59926,7 @@
         <v>45215</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59999,7 +59999,7 @@
         <v>45089</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>44893</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>44517</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -60218,7 +60218,7 @@
         <v>45610</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -60291,7 +60291,7 @@
         <v>45351</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -60364,7 +60364,7 @@
         <v>44543</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -60437,7 +60437,7 @@
         <v>44603</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45183</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>44691</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>44831</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60734,7 +60734,7 @@
         <v>44110</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60812,7 +60812,7 @@
         <v>43938</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60885,7 +60885,7 @@
         <v>44825</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45188</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -61036,7 +61036,7 @@
         <v>44959</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -61109,7 +61109,7 @@
         <v>45373</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -61182,7 +61182,7 @@
         <v>44959</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -61255,7 +61255,7 @@
         <v>45155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -61328,7 +61328,7 @@
         <v>45611</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -61401,7 +61401,7 @@
         <v>45271</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -61474,7 +61474,7 @@
         <v>45474</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -61547,7 +61547,7 @@
         <v>45646</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>45734</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61693,7 +61693,7 @@
         <v>45702</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61766,7 +61766,7 @@
         <v>45719</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61839,7 +61839,7 @@
         <v>45734</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>45460</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61985,7 +61985,7 @@
         <v>46064</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -62058,7 +62058,7 @@
         <v>46070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -62131,7 +62131,7 @@
         <v>46097</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -62204,7 +62204,7 @@
         <v>46099</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -62277,7 +62277,7 @@
         <v>46099</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>46105</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -62423,7 +62423,7 @@
         <v>46164</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -62496,7 +62496,7 @@
         <v>44972</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -62569,7 +62569,7 @@
         <v>44960</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62642,7 +62642,7 @@
         <v>45250</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>44981</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62788,7 +62788,7 @@
         <v>46045</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62861,7 +62861,7 @@
         <v>46260</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
